--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -970,7 +970,7 @@
         <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
         <v>1.84</v>
@@ -997,10 +997,10 @@
         <v>1.67</v>
       </c>
       <c r="Z4">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AA4">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="AB4">
         <v>1.36</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P8">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="AA8">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="AB8">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>4.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AB9">
+        <v>1.57</v>
+      </c>
+      <c r="AC9">
+        <v>4.15</v>
+      </c>
+      <c r="AD9">
+        <v>1.16</v>
+      </c>
+      <c r="AE9">
+        <v>1.01</v>
+      </c>
+      <c r="AF9">
+        <v>1.94</v>
+      </c>
+      <c r="AG9">
         <v>1.77</v>
       </c>
-      <c r="AC9">
-        <v>3.34</v>
-      </c>
-      <c r="AD9">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.27</v>
       </c>
-      <c r="AE9">
-        <v>1.05</v>
-      </c>
-      <c r="AF9">
-        <v>1.92</v>
-      </c>
-      <c r="AG9">
-        <v>1.79</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.19</v>
-      </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
         <v>2.15</v>
@@ -2935,7 +2935,7 @@
         <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
         <v>2.88</v>
@@ -2944,7 +2944,7 @@
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.06</v>
@@ -3587,7 +3587,7 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
         <v>2.6</v>
@@ -3608,7 +3608,7 @@
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3771,16 +3771,16 @@
         <v>4.6</v>
       </c>
       <c r="AA21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AC21">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
         <v>3.85</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S22">
         <v>1.27</v>
@@ -3928,7 +3928,7 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
         <v>4.49</v>
@@ -4067,31 +4067,31 @@
         <v>1.45</v>
       </c>
       <c r="Q23">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
         <v>4.2</v>
@@ -4109,7 +4109,7 @@
         <v>1.37</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
         <v>1.8</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
         <v>1.16</v>
@@ -4396,7 +4396,7 @@
         <v>3.36</v>
       </c>
       <c r="R25">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S25">
         <v>1.5</v>
@@ -4411,16 +4411,16 @@
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
         <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z25">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA25">
         <v>2.45</v>
@@ -4429,19 +4429,19 @@
         <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="AD25">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG25">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
         <v>1.83</v>
@@ -4713,10 +4713,10 @@
         <v>2.02</v>
       </c>
       <c r="O27">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="P27">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -5057,7 +5057,7 @@
         <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
         <v>1.53</v>
@@ -5081,10 +5081,10 @@
         <v>2.16</v>
       </c>
       <c r="AC29">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
         <v>1.17</v>
@@ -5531,25 +5531,25 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q32">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R32">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="S32">
         <v>1.11</v>
       </c>
       <c r="T32">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="U32">
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="W32">
         <v>1.25</v>
@@ -5558,7 +5558,7 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
         <v>8.300000000000001</v>
@@ -5598,7 +5598,7 @@
         <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>4.14</v>
+        <v>5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5857,7 +5857,7 @@
         <v>4.33</v>
       </c>
       <c r="P34">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Q34">
         <v>1.85</v>
@@ -5896,7 +5896,7 @@
         <v>2.45</v>
       </c>
       <c r="AC34">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AD34">
         <v>1.54</v>
@@ -6020,31 +6020,31 @@
         <v>4</v>
       </c>
       <c r="P35">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
         <v>2.43</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.22</v>
@@ -6053,25 +6053,25 @@
         <v>3.55</v>
       </c>
       <c r="AA35">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC35">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF35">
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6352,10 +6352,10 @@
         <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
         <v>3.6</v>
@@ -7327,7 +7327,7 @@
         <v>15</v>
       </c>
       <c r="Q43">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R43">
         <v>2.8</v>
@@ -7339,13 +7339,13 @@
         <v>3.4</v>
       </c>
       <c r="U43">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7354,7 +7354,7 @@
         <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
       <c r="AA43">
         <v>1.57</v>
@@ -7363,7 +7363,7 @@
         <v>2.38</v>
       </c>
       <c r="AC43">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD43">
         <v>1.5</v>
@@ -7487,10 +7487,10 @@
         <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q44">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7502,7 +7502,7 @@
         <v>2.88</v>
       </c>
       <c r="U44">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="V44">
         <v>1.4</v>
@@ -7554,7 +7554,7 @@
         <v>1.5</v>
       </c>
       <c r="AK44">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,16 +7647,16 @@
         <v>1.36</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
         <v>7.2</v>
       </c>
       <c r="Q45">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S45">
         <v>1.26</v>
@@ -7671,7 +7671,7 @@
         <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7698,7 +7698,7 @@
         <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG45">
         <v>1.88</v>
@@ -7828,10 +7828,10 @@
         <v>3.98</v>
       </c>
       <c r="U46">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W46">
         <v>1.17</v>
@@ -7991,7 +7991,7 @@
         <v>4.9</v>
       </c>
       <c r="U47">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V47">
         <v>1.85</v>
@@ -9298,13 +9298,13 @@
         <v>2.16</v>
       </c>
       <c r="V55">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W55">
         <v>1.13</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
         <v>1.18</v>
@@ -9316,7 +9316,7 @@
         <v>1.48</v>
       </c>
       <c r="AB55">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
         <v>2.4</v>
@@ -9331,7 +9331,7 @@
         <v>2</v>
       </c>
       <c r="AG55">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9452,10 +9452,10 @@
         <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U56">
         <v>2.5</v>
@@ -9464,7 +9464,7 @@
         <v>1.47</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9476,7 +9476,7 @@
         <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB56">
         <v>1.98</v>
@@ -9488,7 +9488,7 @@
         <v>1.37</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.6</v>
@@ -9953,7 +9953,7 @@
         <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
         <v>1.03</v>
@@ -9977,7 +9977,7 @@
         <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
         <v>1.89</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O60">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="Q60">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R60">
         <v>2.4</v>
@@ -10110,7 +10110,7 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V60">
         <v>1.49</v>
@@ -10125,13 +10125,13 @@
         <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AA60">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC60">
         <v>2.8</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK60">
         <v>2.75</v>
@@ -11242,10 +11242,10 @@
         <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
         <v>3.19</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="R8">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
+        <v>1.57</v>
+      </c>
+      <c r="AC8">
+        <v>4.15</v>
+      </c>
+      <c r="AD8">
+        <v>1.16</v>
+      </c>
+      <c r="AE8">
+        <v>1.01</v>
+      </c>
+      <c r="AF8">
+        <v>1.94</v>
+      </c>
+      <c r="AG8">
         <v>1.77</v>
       </c>
-      <c r="AC8">
-        <v>3.34</v>
-      </c>
-      <c r="AD8">
-        <v>1.27</v>
-      </c>
-      <c r="AE8">
-        <v>1.05</v>
-      </c>
-      <c r="AF8">
-        <v>1.92</v>
-      </c>
-      <c r="AG8">
-        <v>1.79</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="Q9">
-        <v>2.69</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>2.59</v>
+        <v>3.21</v>
       </c>
       <c r="AA9">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="R12">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="S12">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="U12">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="V12">
+        <v>1.35</v>
+      </c>
+      <c r="W12">
+        <v>1.04</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
         <v>1.31</v>
       </c>
-      <c r="W12">
-        <v>1.02</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.35</v>
-      </c>
       <c r="Z12">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AA12">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AB12">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AK12">
         <v>1.3</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="O15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2974,7 +2974,7 @@
         <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
         <v>3.35</v>
       </c>
       <c r="P17">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>5.02</v>
+        <v>4.33</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S17">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
         <v>2.82</v>
@@ -3119,10 +3119,10 @@
         <v>3.08</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB17">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>3.42</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="V19">
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG19">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3590,10 +3590,10 @@
         <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3608,7 +3608,7 @@
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3735,10 +3735,10 @@
         <v>1.21</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q21">
         <v>1.63</v>
@@ -3765,13 +3765,13 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
         <v>2.32</v>
@@ -3780,10 +3780,10 @@
         <v>2.53</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
         <v>2.32</v>
@@ -3937,19 +3937,19 @@
         <v>1.62</v>
       </c>
       <c r="AB22">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC22">
         <v>2.43</v>
       </c>
       <c r="AD22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE22">
         <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
         <v>2.34</v>
@@ -4598,7 +4598,7 @@
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.83</v>
@@ -4924,7 +4924,7 @@
         <v>1.24</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.85</v>
@@ -5045,22 +5045,22 @@
         <v>2.62</v>
       </c>
       <c r="Q29">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
         <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
         <v>1.08</v>
@@ -5069,7 +5069,7 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
         <v>4.33</v>
@@ -5084,7 +5084,7 @@
         <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
         <v>1.17</v>
@@ -6210,7 +6210,7 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
         <v>4.4</v>
@@ -6219,7 +6219,7 @@
         <v>1.63</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC36">
         <v>2.46</v>
@@ -6228,10 +6228,10 @@
         <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
         <v>2.25</v>
@@ -6367,7 +6367,7 @@
         <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6382,10 +6382,10 @@
         <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD37">
         <v>1.51</v>
@@ -7191,7 +7191,7 @@
         <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
@@ -7333,7 +7333,7 @@
         <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
         <v>3.4</v>
@@ -7345,7 +7345,7 @@
         <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -8139,19 +8139,19 @@
         <v>2.82</v>
       </c>
       <c r="P48">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q48">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="R48">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="S48">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T48">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U48">
         <v>3.75</v>
@@ -8166,31 +8166,31 @@
         <v>1.08</v>
       </c>
       <c r="Y48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z48">
         <v>2.25</v>
       </c>
       <c r="AA48">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AB48">
         <v>1.4</v>
       </c>
       <c r="AC48">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AD48">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AG48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>1.34</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
         <v>1.04</v>
@@ -8335,7 +8335,7 @@
         <v>3.1</v>
       </c>
       <c r="AA49">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB49">
         <v>1.67</v>
@@ -8353,7 +8353,7 @@
         <v>1.74</v>
       </c>
       <c r="AG49">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AK49">
         <v>1.3</v>
@@ -8459,25 +8459,25 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q50">
         <v>3.25</v>
       </c>
       <c r="R50">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50">
         <v>2.55</v>
@@ -8486,10 +8486,10 @@
         <v>1.42</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>3.3</v>
+        <v>3.69</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.3</v>
@@ -8661,7 +8661,7 @@
         <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB51">
         <v>1.95</v>
@@ -8670,16 +8670,16 @@
         <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>4.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q52">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="R52">
         <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W52">
+        <v>1.06</v>
+      </c>
+      <c r="X52">
+        <v>1.04</v>
+      </c>
+      <c r="Y52">
+        <v>1.24</v>
+      </c>
+      <c r="Z52">
+        <v>3.74</v>
+      </c>
+      <c r="AA52">
+        <v>1.76</v>
+      </c>
+      <c r="AB52">
+        <v>2.02</v>
+      </c>
+      <c r="AC52">
+        <v>2.76</v>
+      </c>
+      <c r="AD52">
+        <v>1.4</v>
+      </c>
+      <c r="AE52">
         <v>1.1</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.25</v>
-      </c>
-      <c r="Z52">
-        <v>3.65</v>
-      </c>
-      <c r="AA52">
-        <v>1.9</v>
-      </c>
-      <c r="AB52">
-        <v>1.87</v>
-      </c>
-      <c r="AC52">
-        <v>3.22</v>
-      </c>
-      <c r="AD52">
-        <v>1.28</v>
-      </c>
-      <c r="AE52">
-        <v>1.07</v>
-      </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>4.3</v>
       </c>
       <c r="Q53">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC53">
-        <v>2.76</v>
+        <v>3.29</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -9126,34 +9126,34 @@
         <v>2.15</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
         <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA54">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB54">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
@@ -9165,7 +9165,7 @@
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
         <v>2</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9440,10 +9440,10 @@
         <v>2.4</v>
       </c>
       <c r="O56">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="Q56">
         <v>2.8</v>
@@ -9615,25 +9615,25 @@
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
         <v>3.4</v>
       </c>
       <c r="U57">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
         <v>5</v>
@@ -9648,7 +9648,7 @@
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
@@ -10267,49 +10267,49 @@
         <v>2.23</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U61">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V61">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AA61">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB61">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC61">
         <v>2.88</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG61">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10587,25 +10587,25 @@
         <v>3.1</v>
       </c>
       <c r="Q63">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R63">
         <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="V63">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
         <v>1.08</v>
@@ -10617,16 +10617,16 @@
         <v>2.75</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC63">
         <v>4.33</v>
       </c>
       <c r="AD63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE63">
         <v>1.06</v>
@@ -10635,7 +10635,7 @@
         <v>1.91</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK63">
         <v>1.53</v>
@@ -10750,10 +10750,10 @@
         <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R64">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="S64">
         <v>1.45</v>
@@ -10774,19 +10774,19 @@
         <v>1.07</v>
       </c>
       <c r="Y64">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z64">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA64">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AB64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC64">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD64">
         <v>1.13</v>
@@ -10798,7 +10798,7 @@
         <v>2.05</v>
       </c>
       <c r="AG64">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11245,7 +11245,7 @@
         <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T67">
         <v>3.19</v>
@@ -11257,7 +11257,7 @@
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.04</v>
@@ -11417,7 +11417,7 @@
         <v>2.36</v>
       </c>
       <c r="V68">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
         <v>1.09</v>
@@ -11426,19 +11426,19 @@
         <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
         <v>3.9</v>
       </c>
       <c r="AA68">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB68">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC68">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD68">
         <v>1.36</v>
@@ -11580,10 +11580,10 @@
         <v>3.3</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
         <v>1.05</v>
@@ -11595,10 +11595,10 @@
         <v>2.62</v>
       </c>
       <c r="AA69">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB69">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC69">
         <v>4.4</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q30">
         <v>3.46</v>
@@ -5214,16 +5214,16 @@
         <v>2.33</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
         <v>2.59</v>
       </c>
       <c r="V30">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5235,7 +5235,7 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
         <v>1.67</v>
@@ -5256,7 +5256,7 @@
         <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q31">
         <v>2.95</v>
@@ -5435,7 +5435,7 @@
         <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>9.5</v>
       </c>
       <c r="Q32">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R32">
         <v>3.2</v>
@@ -5543,7 +5543,7 @@
         <v>1.11</v>
       </c>
       <c r="T32">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U32">
         <v>1.75</v>
@@ -5694,7 +5694,7 @@
         <v>3.95</v>
       </c>
       <c r="P33">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="R41">
         <v>2.38</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T41">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="U41">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7025,7 +7025,7 @@
         <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
         <v>3.5</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>2.38</v>
       </c>
       <c r="Q44">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7502,7 +7502,7 @@
         <v>2.88</v>
       </c>
       <c r="U44">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="V44">
         <v>1.4</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O58">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="P58">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q58">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R58">
         <v>3.22</v>
@@ -9781,13 +9781,13 @@
         <v>1.12</v>
       </c>
       <c r="T58">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V58">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="W58">
         <v>1.29</v>
@@ -10913,7 +10913,7 @@
         <v>6.95</v>
       </c>
       <c r="Q65">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R65">
         <v>2.4</v>
@@ -10925,10 +10925,10 @@
         <v>3.28</v>
       </c>
       <c r="U65">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W65">
         <v>1.1</v>
@@ -10955,7 +10955,7 @@
         <v>1.43</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
         <v>1.83</v>
@@ -11414,7 +11414,7 @@
         <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="V68">
         <v>1.48</v>
@@ -11435,16 +11435,16 @@
         <v>1.68</v>
       </c>
       <c r="AB68">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD68">
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
         <v>1.85</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -8136,13 +8136,13 @@
         <v>2.1</v>
       </c>
       <c r="O48">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P48">
         <v>3.8</v>
       </c>
       <c r="Q48">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="R48">
         <v>1.77</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q50">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="R50">
         <v>2.2</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA50">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB50">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD50">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q51">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z51">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AD51">
         <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P52">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="Q52">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V52">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AC52">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
         <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
         <v>1.62</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -964,7 +964,7 @@
         <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="P4">
         <v>3.1</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1619,19 +1619,19 @@
         <v>2.95</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="R8">
         <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T8">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
         <v>3.28</v>
@@ -1646,16 +1646,16 @@
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
         <v>2.59</v>
       </c>
       <c r="AA8">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
         <v>4.15</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.42</v>
+        <v>4.85</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
         <v>2.09</v>
@@ -1809,22 +1809,22 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3.21</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
         <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
         <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
         <v>1.05</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
         <v>1.95</v>
@@ -1987,7 +1987,7 @@
         <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="R12">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA12">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
+        <v>1.86</v>
+      </c>
+      <c r="AG12">
         <v>1.82</v>
-      </c>
-      <c r="AG12">
-        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2781,7 +2781,7 @@
         <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2805,7 +2805,7 @@
         <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
         <v>1.72</v>
@@ -2923,10 +2923,10 @@
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2959,7 +2959,7 @@
         <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
@@ -2971,10 +2971,10 @@
         <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
         <v>3.35</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q17">
-        <v>4.33</v>
+        <v>4.91</v>
       </c>
       <c r="R17">
         <v>2.03</v>
@@ -3101,7 +3101,7 @@
         <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>3.21</v>
       </c>
       <c r="V17">
         <v>1.37</v>
@@ -3119,10 +3119,10 @@
         <v>3.08</v>
       </c>
       <c r="AA17">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
         <v>3.42</v>
@@ -3131,7 +3131,7 @@
         <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
         <v>1.81</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>3.8</v>
       </c>
       <c r="Q19">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R19">
         <v>2.1</v>
@@ -3427,13 +3427,13 @@
         <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V19">
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3463,7 +3463,7 @@
         <v>1.93</v>
       </c>
       <c r="AG19">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3608,7 +3608,7 @@
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3771,16 +3771,16 @@
         <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
         <v>2.32</v>
       </c>
       <c r="AC21">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
         <v>1.15</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S22">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
         <v>2.29</v>
@@ -3925,13 +3925,13 @@
         <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AA22">
         <v>1.62</v>
@@ -4061,10 +4061,10 @@
         <v>5.5</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="P23">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q23">
         <v>5.75</v>
@@ -4076,7 +4076,7 @@
         <v>1.32</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
         <v>2.53</v>
@@ -4085,10 +4085,10 @@
         <v>1.46</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.23</v>
@@ -4106,10 +4106,10 @@
         <v>2.68</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.8</v>
@@ -4131,7 +4131,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>2.8</v>
       </c>
       <c r="P25">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
         <v>3.36</v>
@@ -4399,16 +4399,16 @@
         <v>1.95</v>
       </c>
       <c r="S25">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
         <v>1.01</v>
@@ -4429,19 +4429,19 @@
         <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
         <v>1.19</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="O27">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
         <v>3.76</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -4903,7 +4903,7 @@
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.33</v>
@@ -4915,22 +4915,22 @@
         <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AD28">
         <v>1.24</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
         <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="Q35">
         <v>1.95</v>
@@ -6041,7 +6041,7 @@
         <v>1.49</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6059,7 +6059,7 @@
         <v>2.02</v>
       </c>
       <c r="AC35">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD35">
         <v>1.34</v>
@@ -6071,7 +6071,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AK35">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6189,13 +6189,13 @@
         <v>3.8</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
         <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U36">
         <v>2.2</v>
@@ -6210,7 +6210,7 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
         <v>4.4</v>
@@ -6222,13 +6222,13 @@
         <v>2.23</v>
       </c>
       <c r="AC36">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
         <v>1.53</v>
@@ -6346,7 +6346,7 @@
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6376,7 +6376,7 @@
         <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA37">
         <v>1.57</v>
@@ -6385,7 +6385,7 @@
         <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AD37">
         <v>1.51</v>
@@ -6413,7 +6413,7 @@
         <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -7179,7 +7179,7 @@
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W42">
         <v>1.1</v>
@@ -7191,7 +7191,7 @@
         <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="O43">
         <v>5.75</v>
       </c>
       <c r="P43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q43">
         <v>1.6</v>
@@ -7336,16 +7336,16 @@
         <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V43">
         <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7554,7 +7554,7 @@
         <v>1.5</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P45">
-        <v>7.2</v>
+        <v>6.65</v>
       </c>
       <c r="Q45">
         <v>1.88</v>
@@ -7662,7 +7662,7 @@
         <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U45">
         <v>2.38</v>
@@ -7671,10 +7671,10 @@
         <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
@@ -7689,16 +7689,16 @@
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AD45">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF45">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG45">
         <v>1.88</v>
@@ -7864,7 +7864,7 @@
         <v>1.36</v>
       </c>
       <c r="AG46">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -8003,10 +8003,10 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z47">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA47">
         <v>1.31</v>
@@ -8314,10 +8314,10 @@
         <v>1.45</v>
       </c>
       <c r="T49">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="V49">
         <v>1.34</v>
@@ -8341,7 +8341,7 @@
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD49">
         <v>1.25</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O54">
         <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -9129,10 +9129,10 @@
         <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U54">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V54">
         <v>1.42</v>
@@ -9159,13 +9159,13 @@
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG54">
         <v>2</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9280,7 +9280,7 @@
         <v>6.25</v>
       </c>
       <c r="P55">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -9328,7 +9328,7 @@
         <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG55">
         <v>1.77</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9606,7 +9606,7 @@
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9615,25 +9615,25 @@
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
         <v>3.4</v>
       </c>
       <c r="U57">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
         <v>5</v>
@@ -9769,10 +9769,10 @@
         <v>6.2</v>
       </c>
       <c r="P58">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q58">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R58">
         <v>3.22</v>
@@ -9784,10 +9784,10 @@
         <v>5</v>
       </c>
       <c r="U58">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V58">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="W58">
         <v>1.29</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O59">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q59">
         <v>3.3</v>
@@ -9956,7 +9956,7 @@
         <v>1.07</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y59">
         <v>1.4</v>
@@ -10104,7 +10104,7 @@
         <v>2.4</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
         <v>3.3</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
         <v>2.87</v>
@@ -10780,25 +10780,25 @@
         <v>2.35</v>
       </c>
       <c r="AA64">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AB64">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC64">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD64">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG64">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11414,7 +11414,7 @@
         <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="V68">
         <v>1.48</v>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="R69">
         <v>1.91</v>
@@ -11589,13 +11589,13 @@
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z69">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="AA69">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AB69">
         <v>1.57</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
         <v>2.6</v>
@@ -2446,7 +2446,7 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
         <v>2.73</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
         <v>1.4</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q31">
         <v>2.95</v>
@@ -5435,7 +5435,7 @@
         <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.17</v>
       </c>
       <c r="O32">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="P32">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q32">
         <v>1.45</v>
@@ -5540,16 +5540,16 @@
         <v>3.2</v>
       </c>
       <c r="S32">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T32">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="U32">
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W32">
         <v>1.25</v>
@@ -5573,7 +5573,7 @@
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AE32">
         <v>1.5</v>
@@ -5694,7 +5694,7 @@
         <v>3.95</v>
       </c>
       <c r="P33">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -5893,7 +5893,7 @@
         <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
         <v>2.28</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8462,10 +8462,10 @@
         <v>2.87</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q50">
         <v>3.69</v>
@@ -8489,7 +8489,7 @@
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.21</v>
@@ -8516,7 +8516,7 @@
         <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8625,22 +8625,22 @@
         <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
         <v>3.35</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.4</v>
@@ -8655,10 +8655,10 @@
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
         <v>1.76</v>
@@ -8673,13 +8673,13 @@
         <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>2.8</v>
       </c>
       <c r="O52">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
         <v>2.16</v>
@@ -8797,13 +8797,13 @@
         <v>3.25</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U52">
         <v>2.55</v>
@@ -8954,13 +8954,13 @@
         <v>3.4</v>
       </c>
       <c r="P53">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q53">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R53">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
         <v>1.36</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q61">
         <v>2.5</v>
@@ -10306,10 +10306,10 @@
         <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="O65">
         <v>4.75</v>
       </c>
       <c r="P65">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="Q65">
         <v>1.83</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O66">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
         <v>1.62</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
         <v>1.57</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3590,10 +3590,10 @@
         <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,7 +3602,7 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
         <v>3.8</v>
@@ -3771,10 +3771,10 @@
         <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
         <v>2.75</v>
@@ -3898,16 +3898,16 @@
         <v>2.3</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3928,13 +3928,13 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z22">
         <v>4.5</v>
       </c>
       <c r="AA22">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB22">
         <v>2.18</v>
@@ -3946,7 +3946,7 @@
         <v>1.46</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF22">
         <v>1.44</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="Q26">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R26">
         <v>2.1</v>
@@ -4568,10 +4568,10 @@
         <v>2.63</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
         <v>3.76</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
         <v>2.62</v>
@@ -5057,7 +5057,7 @@
         <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="V29">
         <v>1.5</v>
@@ -5084,7 +5084,7 @@
         <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
         <v>1.17</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6385,7 +6385,7 @@
         <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD37">
         <v>1.51</v>
@@ -8311,19 +8311,19 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T49">
         <v>2.75</v>
       </c>
       <c r="U49">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="V49">
         <v>1.34</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.04</v>
@@ -8341,7 +8341,7 @@
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
         <v>1.25</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O55">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="P55">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
       </c>
       <c r="R55">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="S55">
         <v>1.27</v>
@@ -9313,7 +9313,7 @@
         <v>5</v>
       </c>
       <c r="AA55">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB55">
         <v>2.35</v>
@@ -9328,7 +9328,7 @@
         <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG55">
         <v>1.77</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O57">
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9615,7 +9615,7 @@
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
         <v>3.4</v>
@@ -9627,7 +9627,7 @@
         <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9636,7 +9636,7 @@
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA57">
         <v>1.6</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="O2">
-        <v>4.7</v>
+        <v>5.35</v>
       </c>
       <c r="P2">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>5.68</v>
+        <v>5.74</v>
       </c>
       <c r="R3">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
+        <v>1.4</v>
+      </c>
+      <c r="T3">
+        <v>2.8</v>
+      </c>
+      <c r="U3">
+        <v>2.8</v>
+      </c>
+      <c r="V3">
         <v>1.36</v>
-      </c>
-      <c r="T3">
-        <v>2.88</v>
-      </c>
-      <c r="U3">
-        <v>2.88</v>
-      </c>
-      <c r="V3">
-        <v>1.33</v>
       </c>
       <c r="W3">
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB3">
+        <v>1.72</v>
+      </c>
+      <c r="AC3">
+        <v>3.34</v>
+      </c>
+      <c r="AD3">
+        <v>1.24</v>
+      </c>
+      <c r="AE3">
+        <v>1.08</v>
+      </c>
+      <c r="AF3">
+        <v>1.95</v>
+      </c>
+      <c r="AG3">
         <v>1.75</v>
       </c>
-      <c r="AC3">
-        <v>3.42</v>
-      </c>
-      <c r="AD3">
-        <v>1.23</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
-      <c r="AF3">
-        <v>1.96</v>
-      </c>
-      <c r="AG3">
-        <v>1.73</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
         <v>1.1</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA6">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB7">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AD7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O8">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AB8">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>4.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="AB9">
+        <v>1.58</v>
+      </c>
+      <c r="AC9">
+        <v>4.15</v>
+      </c>
+      <c r="AD9">
+        <v>1.16</v>
+      </c>
+      <c r="AE9">
+        <v>1.01</v>
+      </c>
+      <c r="AF9">
+        <v>1.94</v>
+      </c>
+      <c r="AG9">
         <v>1.77</v>
       </c>
-      <c r="AC9">
-        <v>3.34</v>
-      </c>
-      <c r="AD9">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.27</v>
       </c>
-      <c r="AE9">
-        <v>1.05</v>
-      </c>
-      <c r="AF9">
-        <v>1.92</v>
-      </c>
-      <c r="AG9">
-        <v>1.79</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
-      </c>
       <c r="AK9">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -2283,10 +2283,10 @@
         <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U12">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="V12">
         <v>1.32</v>
@@ -2304,13 +2304,13 @@
         <v>2.81</v>
       </c>
       <c r="AA12">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="AD12">
         <v>1.2</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
         <v>2.6</v>
@@ -2446,13 +2446,13 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2467,7 +2467,7 @@
         <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
         <v>1.81</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2923,7 +2923,7 @@
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
         <v>3.95</v>
@@ -2953,13 +2953,13 @@
         <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="AA16">
         <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O17">
         <v>3.35</v>
       </c>
       <c r="P17">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>4.91</v>
+        <v>4.33</v>
       </c>
       <c r="R17">
         <v>2.03</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
         <v>2.82</v>
       </c>
       <c r="U17">
-        <v>3.21</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
         <v>1.37</v>
@@ -3119,10 +3119,10 @@
         <v>3.08</v>
       </c>
       <c r="AA17">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
         <v>3.42</v>
@@ -3131,13 +3131,13 @@
         <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
         <v>1.81</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3771,16 +3771,16 @@
         <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
         <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
         <v>1.15</v>
@@ -4058,37 +4058,37 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O23">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Q23">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.23</v>
@@ -4097,7 +4097,7 @@
         <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
         <v>2.1</v>
@@ -4106,7 +4106,7 @@
         <v>2.68</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q24">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="R24">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V24">
         <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB24">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AC24">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD24">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
+        <v>1.82</v>
+      </c>
+      <c r="AG24">
         <v>1.85</v>
       </c>
-      <c r="AG24">
-        <v>1.82</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK24">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
         <v>1.99</v>
@@ -4894,7 +4894,7 @@
         <v>2.75</v>
       </c>
       <c r="U28">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="V28">
         <v>1.3</v>
@@ -4930,7 +4930,7 @@
         <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>2.62</v>
@@ -5057,13 +5057,13 @@
         <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="V29">
         <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
         <v>1.04</v>
@@ -5220,10 +5220,10 @@
         <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5235,7 +5235,7 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
         <v>1.67</v>
@@ -5244,7 +5244,7 @@
         <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="AD30">
         <v>1.48</v>
@@ -5256,7 +5256,7 @@
         <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q31">
         <v>2.95</v>
@@ -5407,7 +5407,7 @@
         <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD31">
         <v>1.42</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O32">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>1.45</v>
@@ -5540,7 +5540,7 @@
         <v>3.2</v>
       </c>
       <c r="S32">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T32">
         <v>4.8</v>
@@ -5549,7 +5549,7 @@
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W32">
         <v>1.25</v>
@@ -5561,7 +5561,7 @@
         <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA32">
         <v>1.21</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O33">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>4.6</v>
+        <v>5.13</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="S33">
         <v>1.29</v>
@@ -5727,7 +5727,7 @@
         <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB33">
         <v>2.25</v>
@@ -5878,7 +5878,7 @@
         <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -6020,13 +6020,13 @@
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6.25</v>
+        <v>5.7</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S35">
         <v>1.3</v>
@@ -6038,10 +6038,10 @@
         <v>2.43</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6053,10 +6053,10 @@
         <v>3.55</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC35">
         <v>2.8</v>
@@ -6065,7 +6065,7 @@
         <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
         <v>1.85</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
         <v>2.5</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6385,7 +6385,7 @@
         <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
         <v>1.51</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
         <v>1.88</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O41">
         <v>3.45</v>
       </c>
       <c r="P41">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
         <v>2.43</v>
@@ -7010,10 +7010,10 @@
         <v>1.37</v>
       </c>
       <c r="T41">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U41">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
         <v>1.41</v>
@@ -7321,7 +7321,7 @@
         <v>1.06</v>
       </c>
       <c r="O43">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P43">
         <v>14</v>
@@ -7333,28 +7333,28 @@
         <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U43">
         <v>2.27</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="AA43">
         <v>1.57</v>
@@ -7363,7 +7363,7 @@
         <v>2.38</v>
       </c>
       <c r="AC43">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD43">
         <v>1.5</v>
@@ -7484,13 +7484,13 @@
         <v>2.75</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q44">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7647,7 +7647,7 @@
         <v>1.4</v>
       </c>
       <c r="O45">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
         <v>6.65</v>
@@ -7674,7 +7674,7 @@
         <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
@@ -7689,7 +7689,7 @@
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AD45">
         <v>1.45</v>
@@ -7698,7 +7698,7 @@
         <v>1.16</v>
       </c>
       <c r="AF45">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG45">
         <v>1.88</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
         <v>3.85</v>
@@ -7822,7 +7822,7 @@
         <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
         <v>3.98</v>
@@ -7852,10 +7852,10 @@
         <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD46">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE46">
         <v>1.29</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
         <v>2.18</v>
@@ -7985,19 +7985,19 @@
         <v>2.75</v>
       </c>
       <c r="S47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T47">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="U47">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V47">
         <v>1.85</v>
       </c>
       <c r="W47">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8009,7 +8009,7 @@
         <v>8.5</v>
       </c>
       <c r="AA47">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AB47">
         <v>3.3</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="Q52">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
         <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
         <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>3.29</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="Q53">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S53">
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC53">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O54">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -9129,7 +9129,7 @@
         <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U54">
         <v>2.59</v>
@@ -9147,13 +9147,13 @@
         <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AA54">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB54">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O55">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="P55">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -9313,7 +9313,7 @@
         <v>5</v>
       </c>
       <c r="AA55">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB55">
         <v>2.35</v>
@@ -9325,7 +9325,7 @@
         <v>1.56</v>
       </c>
       <c r="AE55">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF55">
         <v>2</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P56">
         <v>2.63</v>
@@ -9766,10 +9766,10 @@
         <v>1.21</v>
       </c>
       <c r="O58">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
       <c r="P58">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q58">
         <v>1.5</v>
@@ -9781,16 +9781,16 @@
         <v>1.12</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U58">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V58">
         <v>1.98</v>
       </c>
       <c r="W58">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X58">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         <v>2.45</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="P59">
         <v>3</v>
@@ -9956,7 +9956,7 @@
         <v>1.07</v>
       </c>
       <c r="X59">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
         <v>1.4</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
         <v>1.45</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P60">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q60">
         <v>1.97</v>
@@ -10110,10 +10110,10 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V60">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10134,10 +10134,10 @@
         <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AD60">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE60">
         <v>1.17</v>
@@ -10162,7 +10162,7 @@
         <v>1.13</v>
       </c>
       <c r="AK60">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -964,7 +964,7 @@
         <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="P4">
         <v>3.1</v>
@@ -985,16 +985,16 @@
         <v>4.3</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z4">
         <v>2.16</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
         <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T10">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1975,7 +1975,7 @@
         <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA10">
         <v>1.77</v>
@@ -1993,10 +1993,10 @@
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2769,7 +2769,7 @@
         <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
         <v>2.88</v>
@@ -2781,7 +2781,7 @@
         <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
         <v>3.14</v>
@@ -2811,7 +2811,7 @@
         <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2926,13 +2926,13 @@
         <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="R16">
         <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T16">
         <v>2.88</v>
@@ -2941,7 +2941,7 @@
         <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
         <v>1.07</v>
@@ -2953,13 +2953,13 @@
         <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
@@ -3246,61 +3246,61 @@
         <v>4.2</v>
       </c>
       <c r="O18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P18">
         <v>1.57</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
         <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,16 +3415,16 @@
         <v>3.8</v>
       </c>
       <c r="Q19">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U19">
         <v>3</v>
@@ -3433,7 +3433,7 @@
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3445,10 +3445,10 @@
         <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC19">
         <v>3.9</v>
@@ -3460,7 +3460,7 @@
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
         <v>1.78</v>
@@ -3907,7 +3907,7 @@
         <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O25">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
         <v>3.36</v>
@@ -4405,13 +4405,13 @@
         <v>2.45</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
         <v>1.07</v>
@@ -4435,7 +4435,7 @@
         <v>1.19</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
         <v>1.96</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
@@ -4598,7 +4598,7 @@
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
         <v>1.83</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4716,7 +4716,7 @@
         <v>3.25</v>
       </c>
       <c r="P27">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>2.17</v>
       </c>
       <c r="Q30">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="R30">
         <v>2.33</v>
@@ -5220,7 +5220,7 @@
         <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
         <v>1.48</v>
@@ -5244,7 +5244,7 @@
         <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AD30">
         <v>1.48</v>
@@ -5374,7 +5374,7 @@
         <v>2.95</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
         <v>1.31</v>
@@ -5407,7 +5407,7 @@
         <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD31">
         <v>1.42</v>
@@ -5435,7 +5435,7 @@
         <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5549,22 +5549,22 @@
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="W32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Z32">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB32">
         <v>3.6</v>
@@ -5573,7 +5573,7 @@
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AE32">
         <v>1.5</v>
@@ -6180,7 +6180,7 @@
         <v>3.4</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
         <v>1.85</v>
@@ -6204,19 +6204,19 @@
         <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA36">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB36">
         <v>2.23</v>
@@ -6225,10 +6225,10 @@
         <v>2.49</v>
       </c>
       <c r="AD36">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
         <v>1.53</v>
@@ -6250,7 +6250,7 @@
         <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7173,13 +7173,13 @@
         <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W42">
         <v>1.1</v>
@@ -7188,28 +7188,28 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
         <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AB42">
         <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG42">
         <v>2.25</v>
@@ -7339,13 +7339,13 @@
         <v>3.4</v>
       </c>
       <c r="U43">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7354,19 +7354,19 @@
         <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="AA43">
         <v>1.57</v>
       </c>
       <c r="AB43">
+        <v>2.25</v>
+      </c>
+      <c r="AC43">
         <v>2.38</v>
       </c>
-      <c r="AC43">
-        <v>2.4</v>
-      </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
         <v>1.18</v>
@@ -7375,7 +7375,7 @@
         <v>2.2</v>
       </c>
       <c r="AG43">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7647,10 +7647,10 @@
         <v>1.4</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="Q45">
         <v>1.88</v>
@@ -7659,7 +7659,7 @@
         <v>2.38</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
         <v>3.22</v>
@@ -7668,13 +7668,13 @@
         <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W45">
         <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
@@ -7683,25 +7683,25 @@
         <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD45">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE45">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
         <v>1.84</v>
       </c>
       <c r="AG45">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8139,22 +8139,22 @@
         <v>2.8</v>
       </c>
       <c r="P48">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q48">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="R48">
         <v>1.77</v>
       </c>
       <c r="S48">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T48">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="U48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V48">
         <v>1.21</v>
@@ -8166,13 +8166,13 @@
         <v>1.08</v>
       </c>
       <c r="Y48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z48">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA48">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB48">
         <v>1.4</v>
@@ -8181,16 +8181,16 @@
         <v>5</v>
       </c>
       <c r="AD48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AG48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
         <v>2.75</v>
@@ -8323,7 +8323,7 @@
         <v>1.34</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
         <v>1.04</v>
@@ -8347,7 +8347,7 @@
         <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
         <v>1.74</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="Q52">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S52">
         <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V52">
         <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC52">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="Q53">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="R53">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC53">
-        <v>2.95</v>
+        <v>3.29</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9440,7 +9440,7 @@
         <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
         <v>2.63</v>
@@ -9482,7 +9482,7 @@
         <v>1.98</v>
       </c>
       <c r="AC56">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD56">
         <v>1.37</v>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
         <v>3.4</v>
@@ -9627,16 +9627,16 @@
         <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA57">
         <v>1.6</v>
@@ -9648,7 +9648,7 @@
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
         <v>3.4</v>
       </c>
       <c r="P61">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q61">
         <v>2.5</v>
@@ -10267,49 +10267,49 @@
         <v>2.23</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T61">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U61">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W61">
+        <v>1.09</v>
+      </c>
+      <c r="X61">
+        <v>1.01</v>
+      </c>
+      <c r="Y61">
+        <v>1.21</v>
+      </c>
+      <c r="Z61">
+        <v>3.58</v>
+      </c>
+      <c r="AA61">
+        <v>1.75</v>
+      </c>
+      <c r="AB61">
+        <v>1.96</v>
+      </c>
+      <c r="AC61">
+        <v>2.74</v>
+      </c>
+      <c r="AD61">
+        <v>1.35</v>
+      </c>
+      <c r="AE61">
         <v>1.1</v>
       </c>
-      <c r="X61">
-        <v>1.03</v>
-      </c>
-      <c r="Y61">
-        <v>1.22</v>
-      </c>
-      <c r="Z61">
-        <v>3.75</v>
-      </c>
-      <c r="AA61">
-        <v>1.73</v>
-      </c>
-      <c r="AB61">
-        <v>2</v>
-      </c>
-      <c r="AC61">
-        <v>2.88</v>
-      </c>
-      <c r="AD61">
-        <v>1.36</v>
-      </c>
-      <c r="AE61">
-        <v>1.13</v>
-      </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG61">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
         <v>3.1</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R63">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
         <v>1.36</v>
@@ -10608,31 +10608,31 @@
         <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z63">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA63">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB63">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC63">
-        <v>4.33</v>
+        <v>3.56</v>
       </c>
       <c r="AD63">
         <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF63">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG63">
         <v>1.8</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O64">
         <v>2.87</v>
@@ -10750,19 +10750,19 @@
         <v>3.2</v>
       </c>
       <c r="Q64">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S64">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T64">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U64">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="V64">
         <v>1.25</v>
@@ -10777,28 +10777,28 @@
         <v>1.5</v>
       </c>
       <c r="Z64">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AA64">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AB64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC64">
         <v>5</v>
       </c>
       <c r="AD64">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG64">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         <v>1.32</v>
       </c>
       <c r="T67">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="U67">
         <v>2.63</v>
@@ -11257,7 +11257,7 @@
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
         <v>1.04</v>
@@ -11281,7 +11281,7 @@
         <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
         <v>1.62</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
         <v>1.57</v>
@@ -11565,37 +11565,37 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="R69">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
         <v>2.53</v>
       </c>
       <c r="U69">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V69">
         <v>1.29</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z69">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA69">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB69">
         <v>1.57</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -816,13 +816,13 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -1480,7 +1480,7 @@
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <v>1.19</v>
@@ -1501,7 +1501,7 @@
         <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.62</v>
@@ -2446,22 +2446,22 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
         <v>3.14</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
         <v>1.49</v>
@@ -2920,13 +2920,13 @@
         <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q16">
-        <v>3.91</v>
+        <v>3.49</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2938,13 +2938,13 @@
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
         <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1.06</v>
@@ -2953,28 +2953,28 @@
         <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.67</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
-        <v>4.95</v>
+        <v>2.46</v>
       </c>
       <c r="R18">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="Z18">
-        <v>5.21</v>
+        <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>2.09</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.79</v>
+        <v>4.25</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>2.42</v>
+        <v>4.64</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="AA19">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="AB19">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="AK19">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>5.5</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q20">
         <v>5.4</v>
@@ -3587,19 +3587,19 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U20">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.2</v>
@@ -3626,7 +3626,7 @@
         <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>1.63</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3765,28 +3765,28 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
         <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC21">
         <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
         <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG21">
         <v>1.57</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK21">
         <v>3.85</v>
@@ -4224,13 +4224,13 @@
         <v>1.59</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
         <v>4.8</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
         <v>2.2</v>
@@ -4251,31 +4251,31 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA24">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG24">
         <v>1.85</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O29">
         <v>3.4</v>
@@ -5048,13 +5048,13 @@
         <v>2.85</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
         <v>2.41</v>
@@ -5084,7 +5084,7 @@
         <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
         <v>1.17</v>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,10 +5208,10 @@
         <v>2.17</v>
       </c>
       <c r="Q30">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S30">
         <v>1.3</v>
@@ -5220,10 +5220,10 @@
         <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5244,7 +5244,7 @@
         <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AD30">
         <v>1.48</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="Q31">
         <v>2.95</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
         <v>1.31</v>
@@ -5528,28 +5528,28 @@
         <v>1.15</v>
       </c>
       <c r="O32">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="P32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q32">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R32">
         <v>3.2</v>
       </c>
       <c r="S32">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T32">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="W32">
         <v>1.29</v>
@@ -5558,22 +5558,22 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA32">
         <v>1.2</v>
       </c>
       <c r="AB32">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC32">
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AE32">
         <v>1.5</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AK32">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P33">
         <v>5.13</v>
@@ -5700,10 +5700,10 @@
         <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
         <v>3.3</v>
@@ -5712,10 +5712,10 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5727,7 +5727,7 @@
         <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB33">
         <v>2.25</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O34">
         <v>4.33</v>
       </c>
       <c r="P34">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="Q34">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R34">
         <v>2.5</v>
@@ -5887,13 +5887,13 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
         <v>2.28</v>
@@ -6180,10 +6180,10 @@
         <v>3.4</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q36">
         <v>3.8</v>
@@ -6210,16 +6210,16 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA36">
         <v>1.7</v>
       </c>
       <c r="AB36">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
         <v>2.49</v>
@@ -6231,7 +6231,7 @@
         <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
         <v>2.25</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
+        <v>1.8</v>
+      </c>
+      <c r="AK36">
         <v>1.24</v>
-      </c>
-      <c r="AK36">
-        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O41">
         <v>3.45</v>
       </c>
       <c r="P41">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q41">
         <v>2.43</v>
@@ -7013,10 +7013,10 @@
         <v>3.07</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7031,7 +7031,7 @@
         <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB41">
         <v>1.85</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -7170,16 +7170,16 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
         <v>3.75</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
         <v>1.1</v>
@@ -7188,13 +7188,13 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
         <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
         <v>2.15</v>
@@ -7209,7 +7209,7 @@
         <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
         <v>2.25</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7532,13 +7532,13 @@
         <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG44">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O46">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q46">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R46">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T46">
-        <v>3.98</v>
+        <v>5.15</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="V46">
+        <v>1.85</v>
+      </c>
+      <c r="W46">
+        <v>1.3</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.06</v>
+      </c>
+      <c r="Z46">
+        <v>8.5</v>
+      </c>
+      <c r="AA46">
+        <v>1.27</v>
+      </c>
+      <c r="AB46">
+        <v>3.3</v>
+      </c>
+      <c r="AC46">
         <v>1.73</v>
       </c>
-      <c r="W46">
-        <v>1.17</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.07</v>
-      </c>
-      <c r="Z46">
-        <v>5.9</v>
-      </c>
-      <c r="AA46">
-        <v>1.36</v>
-      </c>
-      <c r="AB46">
-        <v>2.7</v>
-      </c>
-      <c r="AC46">
-        <v>2.05</v>
-      </c>
       <c r="AD46">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AE46">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AF46">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AG46">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P47">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R47">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S47">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>5.15</v>
+        <v>3.98</v>
       </c>
       <c r="U47">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V47">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W47">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z47">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA47">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AB47">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC47">
+        <v>2.05</v>
+      </c>
+      <c r="AD47">
         <v>1.73</v>
       </c>
-      <c r="AD47">
-        <v>1.96</v>
-      </c>
       <c r="AE47">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AF47">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG47">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,25 +8136,25 @@
         <v>2.1</v>
       </c>
       <c r="O48">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="P48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q48">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="R48">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="S48">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T48">
         <v>2.24</v>
       </c>
       <c r="U48">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V48">
         <v>1.21</v>
@@ -8166,13 +8166,13 @@
         <v>1.08</v>
       </c>
       <c r="Y48">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z48">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AA48">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB48">
         <v>1.4</v>
@@ -8187,10 +8187,10 @@
         <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AG48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U49">
         <v>3.17</v>
@@ -8323,7 +8323,7 @@
         <v>1.34</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
         <v>1.04</v>
@@ -8341,19 +8341,19 @@
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
         <v>1.3</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O50">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q50">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="R50">
         <v>2.2</v>
@@ -8486,10 +8486,10 @@
         <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.21</v>
@@ -8498,7 +8498,7 @@
         <v>3.85</v>
       </c>
       <c r="AA50">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
         <v>1.95</v>
@@ -8507,13 +8507,13 @@
         <v>2.88</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
         <v>2.15</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="R51">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="V51">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AA51">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="Q52">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T52">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V52">
         <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="O53">
         <v>3.4</v>
       </c>
       <c r="P53">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q53">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AC53">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,52 +9114,52 @@
         <v>2.3</v>
       </c>
       <c r="O54">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="U54">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z54">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="AA54">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB54">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
@@ -9283,10 +9283,10 @@
         <v>11</v>
       </c>
       <c r="Q55">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R55">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="S55">
         <v>1.27</v>
@@ -9295,10 +9295,10 @@
         <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
         <v>1.13</v>
@@ -9316,22 +9316,22 @@
         <v>1.5</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC55">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AD55">
         <v>1.56</v>
       </c>
       <c r="AE55">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG55">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="Q56">
         <v>2.8</v>
@@ -9476,7 +9476,7 @@
         <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB56">
         <v>1.98</v>
@@ -9485,7 +9485,7 @@
         <v>2.85</v>
       </c>
       <c r="AD56">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE56">
         <v>1.14</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O57">
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q57">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9633,13 +9633,13 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z57">
         <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB57">
         <v>2.23</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O58">
         <v>6.75</v>
       </c>
       <c r="P58">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q58">
         <v>1.5</v>
@@ -9787,7 +9787,7 @@
         <v>1.67</v>
       </c>
       <c r="V58">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W58">
         <v>1.3</v>
@@ -9836,7 +9836,7 @@
         <v>1.07</v>
       </c>
       <c r="AK58">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="O59">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q59">
         <v>3.3</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="O60">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q60">
         <v>1.97</v>
@@ -10110,7 +10110,7 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V60">
         <v>1.5</v>
@@ -10128,7 +10128,7 @@
         <v>4.2</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB60">
         <v>2.1</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK60">
         <v>2.78</v>
@@ -10255,10 +10255,10 @@
         <v>1.98</v>
       </c>
       <c r="O61">
+        <v>3.25</v>
+      </c>
+      <c r="P61">
         <v>3.4</v>
-      </c>
-      <c r="P61">
-        <v>3.2</v>
       </c>
       <c r="Q61">
         <v>2.5</v>
@@ -10306,10 +10306,10 @@
         <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
         <v>1.62</v>
@@ -10910,13 +10910,13 @@
         <v>4.75</v>
       </c>
       <c r="P65">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="Q65">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S65">
         <v>1.29</v>
@@ -10928,10 +10928,10 @@
         <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10955,7 +10955,7 @@
         <v>1.43</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF65">
         <v>1.83</v>
@@ -11239,10 +11239,10 @@
         <v>2.7</v>
       </c>
       <c r="Q67">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
         <v>1.32</v>
@@ -11251,13 +11251,13 @@
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
         <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.04</v>
@@ -11287,7 +11287,7 @@
         <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O68">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P68">
         <v>6.65</v>
@@ -11414,25 +11414,25 @@
         <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="V68">
         <v>1.48</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA68">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB68">
         <v>2</v>
@@ -11444,7 +11444,7 @@
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
         <v>1.85</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="R38">
         <v>1.93</v>
       </c>
       <c r="S38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U38">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V38">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W38">
         <v>1.06</v>
@@ -6539,28 +6539,28 @@
         <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AA38">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AB38">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC38">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD38">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AG38">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q39">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="R39">
         <v>1.93</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U39">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V39">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W39">
         <v>1.06</v>
@@ -6702,28 +6702,28 @@
         <v>1.41</v>
       </c>
       <c r="Z39">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AA39">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AB39">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC39">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD39">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF39">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8136,22 +8136,22 @@
         <v>2.1</v>
       </c>
       <c r="O48">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="P48">
         <v>3.8</v>
       </c>
       <c r="Q48">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="R48">
         <v>1.85</v>
       </c>
       <c r="S48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T48">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="U48">
         <v>3.6</v>
@@ -8169,28 +8169,28 @@
         <v>1.59</v>
       </c>
       <c r="Z48">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AA48">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AD48">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="Q50">
-        <v>3.74</v>
+        <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U50">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
         <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AA50">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE50">
         <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
+        <v>3.7</v>
+      </c>
+      <c r="Q51">
+        <v>2.36</v>
+      </c>
+      <c r="R51">
         <v>2.3</v>
       </c>
-      <c r="Q51">
-        <v>3.24</v>
-      </c>
-      <c r="R51">
-        <v>2.34</v>
-      </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.07</v>
@@ -8655,31 +8655,31 @@
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z51">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="AA51">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.7</v>
+        <v>2.09</v>
       </c>
       <c r="Q52">
-        <v>2.36</v>
+        <v>3.74</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
+        <v>2.48</v>
+      </c>
+      <c r="V52">
+        <v>1.45</v>
+      </c>
+      <c r="W52">
+        <v>1.11</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.21</v>
+      </c>
+      <c r="Z52">
+        <v>3.85</v>
+      </c>
+      <c r="AA52">
+        <v>1.75</v>
+      </c>
+      <c r="AB52">
+        <v>1.95</v>
+      </c>
+      <c r="AC52">
         <v>2.88</v>
       </c>
-      <c r="V52">
-        <v>1.42</v>
-      </c>
-      <c r="W52">
-        <v>1.07</v>
-      </c>
-      <c r="X52">
-        <v>1.04</v>
-      </c>
-      <c r="Y52">
-        <v>1.24</v>
-      </c>
-      <c r="Z52">
-        <v>3.65</v>
-      </c>
-      <c r="AA52">
-        <v>1.8</v>
-      </c>
-      <c r="AB52">
-        <v>1.9</v>
-      </c>
-      <c r="AC52">
-        <v>3.26</v>
-      </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>2.25</v>
       </c>
       <c r="O63">
+        <v>3.2</v>
+      </c>
+      <c r="P63">
         <v>3.15</v>
-      </c>
-      <c r="P63">
-        <v>3.1</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -10611,31 +10611,31 @@
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z63">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="AA63">
         <v>1.93</v>
       </c>
       <c r="AB63">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC63">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="AD63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
         <v>1.75</v>
       </c>
       <c r="AG63">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O64">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P64">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="Q64">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="R64">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="S64">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T64">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="U64">
         <v>3.6</v>
@@ -10780,10 +10780,10 @@
         <v>2.36</v>
       </c>
       <c r="AA64">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB64">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC64">
         <v>5</v>
@@ -10795,10 +10795,10 @@
         <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG64">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>3.28</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W65">
         <v>1.12</v>
@@ -10937,10 +10937,10 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA65">
         <v>1.66</v>
@@ -10952,16 +10952,16 @@
         <v>2.48</v>
       </c>
       <c r="AD65">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE65">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG65">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P68">
         <v>6.65</v>
@@ -11429,7 +11429,7 @@
         <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA68">
         <v>1.72</v>
@@ -11438,16 +11438,16 @@
         <v>2</v>
       </c>
       <c r="AC68">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AD68">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE68">
         <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG68">
         <v>1.8</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK68">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,16 +11565,16 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
         <v>3</v>
@@ -11589,16 +11589,16 @@
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z69">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA69">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AB69">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC69">
         <v>4.4</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK69">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="O2">
-        <v>5.35</v>
+        <v>4.45</v>
       </c>
       <c r="P2">
-        <v>6.5</v>
+        <v>4.57</v>
       </c>
       <c r="Q2">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="S2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T2">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AA2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB2">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC2">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AD2">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF2">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK2">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2.45</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -985,7 +985,7 @@
         <v>4.3</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
         <v>1.01</v>
@@ -994,7 +994,7 @@
         <v>1.13</v>
       </c>
       <c r="Y4">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="Z4">
         <v>2.16</v>
@@ -1006,7 +1006,7 @@
         <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AD4">
         <v>1.06</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="R8">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T8">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="AD8">
+        <v>1.16</v>
+      </c>
+      <c r="AE8">
+        <v>1.01</v>
+      </c>
+      <c r="AF8">
+        <v>1.94</v>
+      </c>
+      <c r="AG8">
+        <v>1.77</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.27</v>
       </c>
-      <c r="AE8">
-        <v>1.05</v>
-      </c>
-      <c r="AF8">
-        <v>1.92</v>
-      </c>
-      <c r="AG8">
-        <v>1.79</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.15</v>
-      </c>
       <c r="AK8">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>4.42</v>
       </c>
       <c r="Q9">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4387,52 +4387,52 @@
         <v>2.36</v>
       </c>
       <c r="O25">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="P25">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q25">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="R25">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S25">
         <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z25">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AA25">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AB25">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
       <c r="AD25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U51">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O53">
         <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q53">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O63">
+        <v>2.9</v>
+      </c>
+      <c r="P63">
+        <v>4.55</v>
+      </c>
+      <c r="Q63">
+        <v>2.59</v>
+      </c>
+      <c r="R63">
+        <v>1.83</v>
+      </c>
+      <c r="S63">
+        <v>1.4</v>
+      </c>
+      <c r="T63">
+        <v>2.75</v>
+      </c>
+      <c r="U63">
         <v>3.2</v>
       </c>
-      <c r="P63">
-        <v>3.15</v>
-      </c>
-      <c r="Q63">
-        <v>2.88</v>
-      </c>
-      <c r="R63">
-        <v>2.1</v>
-      </c>
-      <c r="S63">
-        <v>1.36</v>
-      </c>
-      <c r="T63">
-        <v>2.88</v>
-      </c>
-      <c r="U63">
-        <v>2.95</v>
-      </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W63">
         <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AA63">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB63">
+        <v>1.68</v>
+      </c>
+      <c r="AC63">
+        <v>3.42</v>
+      </c>
+      <c r="AD63">
+        <v>1.23</v>
+      </c>
+      <c r="AE63">
+        <v>1.07</v>
+      </c>
+      <c r="AF63">
+        <v>1.84</v>
+      </c>
+      <c r="AG63">
+        <v>1.8</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>1.13</v>
+      </c>
+      <c r="AK63">
         <v>1.75</v>
-      </c>
-      <c r="AC63">
-        <v>3.59</v>
-      </c>
-      <c r="AD63">
-        <v>1.25</v>
-      </c>
-      <c r="AE63">
-        <v>1.1</v>
-      </c>
-      <c r="AF63">
-        <v>1.75</v>
-      </c>
-      <c r="AG63">
-        <v>1.97</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.33</v>
-      </c>
-      <c r="AK63">
-        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G64">
@@ -10744,61 +10744,61 @@
         <v>2.25</v>
       </c>
       <c r="O64">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="Q64">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="R64">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="T64">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="U64">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="V64">
+        <v>1.35</v>
+      </c>
+      <c r="W64">
+        <v>1.05</v>
+      </c>
+      <c r="X64">
+        <v>1.03</v>
+      </c>
+      <c r="Y64">
+        <v>1.32</v>
+      </c>
+      <c r="Z64">
+        <v>3.44</v>
+      </c>
+      <c r="AA64">
+        <v>1.93</v>
+      </c>
+      <c r="AB64">
+        <v>1.75</v>
+      </c>
+      <c r="AC64">
+        <v>3.59</v>
+      </c>
+      <c r="AD64">
         <v>1.25</v>
       </c>
-      <c r="W64">
-        <v>1.02</v>
-      </c>
-      <c r="X64">
-        <v>1.07</v>
-      </c>
-      <c r="Y64">
-        <v>1.5</v>
-      </c>
-      <c r="Z64">
-        <v>2.36</v>
-      </c>
-      <c r="AA64">
-        <v>2.38</v>
-      </c>
-      <c r="AB64">
-        <v>1.5</v>
-      </c>
-      <c r="AC64">
-        <v>5</v>
-      </c>
-      <c r="AD64">
-        <v>1.13</v>
-      </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF64">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="P65">
-        <v>6.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q65">
-        <v>1.88</v>
+        <v>3.01</v>
       </c>
       <c r="R65">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="T65">
-        <v>3.28</v>
+        <v>2.51</v>
       </c>
       <c r="U65">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="V65">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
+        <v>1.07</v>
+      </c>
+      <c r="Y65">
+        <v>1.5</v>
+      </c>
+      <c r="Z65">
+        <v>2.36</v>
+      </c>
+      <c r="AA65">
+        <v>2.38</v>
+      </c>
+      <c r="AB65">
+        <v>1.5</v>
+      </c>
+      <c r="AC65">
+        <v>5</v>
+      </c>
+      <c r="AD65">
+        <v>1.13</v>
+      </c>
+      <c r="AE65">
         <v>1.01</v>
       </c>
-      <c r="Y65">
-        <v>1.18</v>
-      </c>
-      <c r="Z65">
-        <v>4.4</v>
-      </c>
-      <c r="AA65">
-        <v>1.66</v>
-      </c>
-      <c r="AB65">
-        <v>2.1</v>
-      </c>
-      <c r="AC65">
-        <v>2.48</v>
-      </c>
-      <c r="AD65">
-        <v>1.47</v>
-      </c>
-      <c r="AE65">
-        <v>1.14</v>
-      </c>
       <c r="AF65">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG65">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>2.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-14 20:00:00</t>
+          <t>2026-09-14 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="P66">
-        <v>2.5</v>
+        <v>6.85</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-14 20:30:00</t>
+          <t>2026-09-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="O68">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>6.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q68">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R68">
         <v>2.3</v>
@@ -11411,10 +11411,10 @@
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V68">
         <v>1.48</v>
@@ -11423,34 +11423,34 @@
         <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
         <v>4.1</v>
       </c>
       <c r="AA68">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC68">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AD68">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>2.63</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-14 21:00:00</t>
+          <t>2026-09-14 20:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,61 +11556,61 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q69">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="R69">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U69">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="V69">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA69">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AC69">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD69">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG69">
         <v>1.8</v>
@@ -11626,41 +11626,367 @@
         </is>
       </c>
       <c r="AJ69">
+        <v>1.08</v>
+      </c>
+      <c r="AK69">
+        <v>2.63</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-09-14 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>3.25</v>
+      </c>
+      <c r="R70">
+        <v>1.87</v>
+      </c>
+      <c r="S70">
+        <v>1.45</v>
+      </c>
+      <c r="T70">
+        <v>2.62</v>
+      </c>
+      <c r="U70">
+        <v>3</v>
+      </c>
+      <c r="V70">
+        <v>1.29</v>
+      </c>
+      <c r="W70">
+        <v>1.04</v>
+      </c>
+      <c r="X70">
+        <v>1.05</v>
+      </c>
+      <c r="Y70">
+        <v>1.38</v>
+      </c>
+      <c r="Z70">
+        <v>2.62</v>
+      </c>
+      <c r="AA70">
+        <v>2.19</v>
+      </c>
+      <c r="AB70">
+        <v>1.61</v>
+      </c>
+      <c r="AC70">
+        <v>4.4</v>
+      </c>
+      <c r="AD70">
+        <v>1.18</v>
+      </c>
+      <c r="AE70">
+        <v>1.02</v>
+      </c>
+      <c r="AF70">
+        <v>1.91</v>
+      </c>
+      <c r="AG70">
+        <v>1.8</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.33</v>
       </c>
-      <c r="AK69">
+      <c r="AK70">
         <v>1.44</v>
       </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-09-14 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Racing United</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>2.3</v>
+      </c>
+      <c r="O71">
+        <v>3.25</v>
+      </c>
+      <c r="P71">
+        <v>2.65</v>
+      </c>
+      <c r="Q71">
+        <v>3.04</v>
+      </c>
+      <c r="R71">
+        <v>1.95</v>
+      </c>
+      <c r="S71">
+        <v>1.39</v>
+      </c>
+      <c r="T71">
+        <v>2.64</v>
+      </c>
+      <c r="U71">
+        <v>2.84</v>
+      </c>
+      <c r="V71">
+        <v>1.34</v>
+      </c>
+      <c r="W71">
+        <v>1.06</v>
+      </c>
+      <c r="X71">
+        <v>1.03</v>
+      </c>
+      <c r="Y71">
+        <v>1.32</v>
+      </c>
+      <c r="Z71">
+        <v>3.07</v>
+      </c>
+      <c r="AA71">
+        <v>2.1</v>
+      </c>
+      <c r="AB71">
+        <v>1.7</v>
+      </c>
+      <c r="AC71">
+        <v>3.8</v>
+      </c>
+      <c r="AD71">
+        <v>1.25</v>
+      </c>
+      <c r="AE71">
+        <v>1.05</v>
+      </c>
+      <c r="AF71">
+        <v>1.78</v>
+      </c>
+      <c r="AG71">
+        <v>1.86</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.33</v>
+      </c>
+      <c r="AK71">
+        <v>1.5</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
         <v>1.25</v>
@@ -1308,7 +1308,7 @@
         <v>3.7</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
         <v>1.57</v>
@@ -1323,13 +1323,13 @@
         <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB6">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC6">
         <v>2.38</v>
@@ -1341,10 +1341,10 @@
         <v>1.22</v>
       </c>
       <c r="AF6">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>3.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -1652,10 +1652,10 @@
         <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
         <v>4.15</v>
@@ -1670,7 +1670,7 @@
         <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>4.42</v>
+        <v>4.74</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
         <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
         <v>2.78</v>
@@ -1815,16 +1815,16 @@
         <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
         <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE9">
         <v>1.05</v>
@@ -1945,16 +1945,16 @@
         <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
         <v>3.1</v>
@@ -1966,7 +1966,7 @@
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -1975,13 +1975,13 @@
         <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC10">
         <v>2.9</v>
@@ -1993,7 +1993,7 @@
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
         <v>2.05</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="O11">
         <v>3.05</v>
@@ -2117,10 +2117,10 @@
         <v>1.88</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
         <v>3.07</v>
@@ -2135,7 +2135,7 @@
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
         <v>2.83</v>
@@ -2144,7 +2144,7 @@
         <v>2.18</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC11">
         <v>3.82</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
         <v>1.35</v>
@@ -2274,22 +2274,22 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.2</v>
+        <v>3.93</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
         <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U12">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -2301,19 +2301,19 @@
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC12">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
@@ -2431,10 +2431,10 @@
         <v>2.4</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -2446,25 +2446,25 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
         <v>1.49</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2769,7 +2769,7 @@
         <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
         <v>2.88</v>
@@ -2778,13 +2778,13 @@
         <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.26</v>
@@ -2793,16 +2793,16 @@
         <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC15">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
         <v>1.1</v>
@@ -2811,7 +2811,7 @@
         <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
         <v>2.06</v>
@@ -2935,16 +2935,16 @@
         <v>1.39</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.06</v>
@@ -2953,28 +2953,28 @@
         <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
         <v>3.35</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q17">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="R17">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AA17">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AB17">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC17">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG17">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q18">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S18">
         <v>1.42</v>
@@ -3264,7 +3264,7 @@
         <v>2.62</v>
       </c>
       <c r="U18">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V18">
         <v>1.33</v>
@@ -3276,31 +3276,31 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
         <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC18">
         <v>3.9</v>
       </c>
       <c r="AD18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
         <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG18">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
         <v>1.83</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.25</v>
+        <v>4.59</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q19">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="R19">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="U19">
         <v>2.2</v>
@@ -3442,28 +3442,28 @@
         <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA19">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB19">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC19">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AD19">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AK19">
         <v>1.17</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="P20">
         <v>1.55</v>
@@ -3587,19 +3587,19 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.2</v>
@@ -3626,7 +3626,7 @@
         <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         <v>1.63</v>
       </c>
       <c r="R21">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
         <v>3.1</v>
@@ -3765,10 +3765,10 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
         <v>1.67</v>
@@ -3786,7 +3786,7 @@
         <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG21">
         <v>1.57</v>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
         <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
         <v>1.52</v>
@@ -3928,28 +3928,28 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
         <v>4.5</v>
       </c>
       <c r="AA22">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB22">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC22">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG22">
         <v>2.34</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>1.53</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.7</v>
+        <v>5.15</v>
       </c>
       <c r="O23">
         <v>4.2</v>
@@ -4076,22 +4076,22 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
         <v>2.55</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
         <v>4.2</v>
@@ -4106,16 +4106,16 @@
         <v>2.68</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
         <v>1.11</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
@@ -4562,10 +4562,10 @@
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="U26">
         <v>2.88</v>
@@ -4574,10 +4574,10 @@
         <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.3</v>
@@ -4601,10 +4601,10 @@
         <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,43 +4710,43 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P27">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA27">
         <v>2.15</v>
@@ -4755,19 +4755,19 @@
         <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -4906,16 +4906,16 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB28">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC28">
         <v>3.39</v>
@@ -4930,7 +4930,7 @@
         <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,22 +5039,22 @@
         <v>2.35</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q29">
         <v>2.85</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
         <v>2.41</v>
@@ -5063,7 +5063,7 @@
         <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
         <v>1.04</v>
@@ -5072,7 +5072,7 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
         <v>1.66</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="R30">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="S30">
         <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
         <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5238,16 +5238,16 @@
         <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>2.86</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AE30">
         <v>1.11</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="Q31">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="R31">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="S31">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
         <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.04</v>
@@ -5410,7 +5410,7 @@
         <v>2.69</v>
       </c>
       <c r="AD31">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
         <v>1.14</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,58 +5525,58 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O32">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="P32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R32">
         <v>3.2</v>
       </c>
       <c r="S32">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V32">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="W32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Z32">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AA32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AB32">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC32">
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AE32">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF32">
         <v>1.7</v>
@@ -5598,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="AK32">
-        <v>5.4</v>
+        <v>4.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="O33">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P33">
-        <v>5.13</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="U33">
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5727,13 +5727,13 @@
         <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
         <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O34">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="P34">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q34">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R34">
         <v>2.5</v>
@@ -5887,13 +5887,13 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA34">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
         <v>2.28</v>
@@ -6017,22 +6017,22 @@
         <v>1.44</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="Q35">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="R35">
-        <v>2.31</v>
+        <v>2.58</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U35">
         <v>2.43</v>
@@ -6050,19 +6050,19 @@
         <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.55</v>
+        <v>3.98</v>
       </c>
       <c r="AA35">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
         <v>1.12</v>
@@ -6071,7 +6071,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
         <v>2.5</v>
@@ -6183,7 +6183,7 @@
         <v>3.7</v>
       </c>
       <c r="P36">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q36">
         <v>3.8</v>
@@ -6204,7 +6204,7 @@
         <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.03</v>
@@ -6216,16 +6216,16 @@
         <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC36">
         <v>2.49</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.24</v>
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="V37">
         <v>1.5</v>
@@ -6373,7 +6373,7 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
         <v>4.6</v>
@@ -6382,16 +6382,16 @@
         <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD37">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q38">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T38">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U38">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V38">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
         <v>1.06</v>
-      </c>
-      <c r="X38">
-        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AA38">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB38">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC38">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AD38">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AG38">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
         <v>1.93</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V39">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y39">
         <v>1.41</v>
       </c>
       <c r="Z39">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AA39">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AB39">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC39">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AD39">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE39">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="Q41">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="R41">
         <v>2.38</v>
@@ -7010,13 +7010,13 @@
         <v>1.37</v>
       </c>
       <c r="T41">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="U41">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7025,22 +7025,22 @@
         <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
         <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC41">
         <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
         <v>1.11</v>
@@ -7049,7 +7049,7 @@
         <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
         <v>3</v>
@@ -7170,13 +7170,13 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
         <v>3.75</v>
       </c>
       <c r="U42">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
         <v>1.62</v>
@@ -7188,28 +7188,28 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AC42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD42">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG42">
         <v>2.25</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
         <v>1.62</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q43">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R43">
         <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7360,13 +7360,13 @@
         <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC43">
         <v>2.38</v>
       </c>
       <c r="AD43">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
         <v>1.18</v>
@@ -7375,7 +7375,7 @@
         <v>2.2</v>
       </c>
       <c r="AG43">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
         <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7499,7 +7499,7 @@
         <v>1.38</v>
       </c>
       <c r="T44">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
         <v>2.75</v>
@@ -7514,7 +7514,7 @@
         <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z44">
         <v>3.15</v>
@@ -7526,16 +7526,16 @@
         <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AD44">
         <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
         <v>2</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="P45">
         <v>6.85</v>
@@ -7659,7 +7659,7 @@
         <v>2.38</v>
       </c>
       <c r="S45">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
         <v>3.22</v>
@@ -7668,7 +7668,7 @@
         <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
         <v>1.07</v>
@@ -7683,25 +7683,25 @@
         <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD45">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
         <v>1.84</v>
       </c>
       <c r="AG45">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -7825,31 +7825,31 @@
         <v>1.11</v>
       </c>
       <c r="T46">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="U46">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V46">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z46">
         <v>8.5</v>
       </c>
       <c r="AA46">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AB46">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC46">
         <v>1.73</v>
@@ -7861,7 +7861,7 @@
         <v>1.4</v>
       </c>
       <c r="AF46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AG46">
         <v>3.2</v>
@@ -7973,10 +7973,10 @@
         <v>2.2</v>
       </c>
       <c r="O47">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="Q47">
         <v>2.55</v>
@@ -7988,13 +7988,13 @@
         <v>1.2</v>
       </c>
       <c r="T47">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U47">
         <v>2</v>
       </c>
       <c r="V47">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W47">
         <v>1.17</v>
@@ -8009,16 +8009,16 @@
         <v>5.9</v>
       </c>
       <c r="AA47">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB47">
         <v>2.7</v>
       </c>
       <c r="AC47">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD47">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE47">
         <v>1.29</v>
@@ -8027,7 +8027,7 @@
         <v>1.36</v>
       </c>
       <c r="AG47">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8314,19 +8314,19 @@
         <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U49">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="V49">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
         <v>1.03</v>
-      </c>
-      <c r="X49">
-        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.36</v>
@@ -8335,25 +8335,25 @@
         <v>3.1</v>
       </c>
       <c r="AA49">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB49">
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="AD49">
         <v>1.22</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG49">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O54">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P54">
         <v>2.8</v>
@@ -9123,19 +9123,19 @@
         <v>3.1</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T54">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U54">
         <v>3</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W54">
         <v>1.05</v>
@@ -9144,7 +9144,7 @@
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z54">
         <v>3.18</v>
@@ -9153,19 +9153,19 @@
         <v>1.97</v>
       </c>
       <c r="AB54">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG54">
         <v>2</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9295,10 +9295,10 @@
         <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W55">
         <v>1.13</v>
@@ -9316,19 +9316,19 @@
         <v>1.5</v>
       </c>
       <c r="AB55">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AC55">
         <v>2.32</v>
       </c>
       <c r="AD55">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AE55">
         <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG55">
         <v>1.75</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="Q56">
         <v>2.8</v>
@@ -9476,7 +9476,7 @@
         <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
         <v>1.98</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
         <v>1.58</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R57">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9624,16 +9624,16 @@
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
         <v>5</v>
@@ -9648,16 +9648,16 @@
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,22 +9763,22 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O58">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="P58">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q58">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R58">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="S58">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T58">
         <v>5.5</v>
@@ -9787,7 +9787,7 @@
         <v>1.67</v>
       </c>
       <c r="V58">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="W58">
         <v>1.3</v>
@@ -9805,7 +9805,7 @@
         <v>1.21</v>
       </c>
       <c r="AB58">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AC58">
         <v>1.63</v>
@@ -9814,7 +9814,7 @@
         <v>2.05</v>
       </c>
       <c r="AE58">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK58">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="Q59">
         <v>3.3</v>
@@ -9941,16 +9941,16 @@
         <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U59">
         <v>3.28</v>
       </c>
       <c r="V59">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
         <v>1.07</v>
@@ -9959,25 +9959,25 @@
         <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z59">
         <v>2.75</v>
       </c>
       <c r="AA59">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AB59">
         <v>1.59</v>
       </c>
       <c r="AC59">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="AD59">
         <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
         <v>1.89</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK59">
         <v>1.45</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P60">
-        <v>6.5</v>
+        <v>7.05</v>
       </c>
       <c r="Q60">
         <v>1.97</v>
@@ -10110,10 +10110,10 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10128,25 +10128,25 @@
         <v>4.2</v>
       </c>
       <c r="AA60">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB60">
         <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE60">
         <v>1.17</v>
       </c>
       <c r="AF60">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG60">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK60">
         <v>2.78</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
+        <v>3.2</v>
+      </c>
+      <c r="P61">
         <v>3.25</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
+        <v>2.7</v>
+      </c>
+      <c r="R61">
+        <v>2.15</v>
+      </c>
+      <c r="S61">
+        <v>1.39</v>
+      </c>
+      <c r="T61">
+        <v>2.7</v>
+      </c>
+      <c r="U61">
+        <v>2.8</v>
+      </c>
+      <c r="V61">
+        <v>1.42</v>
+      </c>
+      <c r="W61">
+        <v>1.08</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.26</v>
+      </c>
+      <c r="Z61">
+        <v>3.2</v>
+      </c>
+      <c r="AA61">
+        <v>1.86</v>
+      </c>
+      <c r="AB61">
+        <v>1.95</v>
+      </c>
+      <c r="AC61">
         <v>3.4</v>
       </c>
-      <c r="Q61">
-        <v>2.5</v>
-      </c>
-      <c r="R61">
-        <v>2.23</v>
-      </c>
-      <c r="S61">
-        <v>1.31</v>
-      </c>
-      <c r="T61">
-        <v>3.02</v>
-      </c>
-      <c r="U61">
-        <v>2.42</v>
-      </c>
-      <c r="V61">
-        <v>1.47</v>
-      </c>
-      <c r="W61">
-        <v>1.09</v>
-      </c>
-      <c r="X61">
-        <v>1.01</v>
-      </c>
-      <c r="Y61">
-        <v>1.21</v>
-      </c>
-      <c r="Z61">
-        <v>3.58</v>
-      </c>
-      <c r="AA61">
-        <v>1.75</v>
-      </c>
-      <c r="AB61">
-        <v>1.96</v>
-      </c>
-      <c r="AC61">
-        <v>2.74</v>
-      </c>
       <c r="AD61">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE61">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG61">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK61">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10774,7 +10774,7 @@
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
         <v>3.44</v>
@@ -10786,19 +10786,19 @@
         <v>1.75</v>
       </c>
       <c r="AC64">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="AD64">
         <v>1.25</v>
       </c>
       <c r="AE64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF64">
         <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -10943,7 +10943,7 @@
         <v>2.36</v>
       </c>
       <c r="AA65">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AB65">
         <v>1.5</v>
@@ -10952,16 +10952,16 @@
         <v>5</v>
       </c>
       <c r="AD65">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE65">
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="O69">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P69">
-        <v>6.65</v>
+        <v>7.6</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -11577,7 +11577,7 @@
         <v>3.2</v>
       </c>
       <c r="U69">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V69">
         <v>1.48</v>
@@ -11589,7 +11589,7 @@
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z69">
         <v>4.1</v>
@@ -11601,16 +11601,16 @@
         <v>2</v>
       </c>
       <c r="AC69">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD69">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG69">
         <v>1.8</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK69">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,16 +11728,16 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R70">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S70">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T70">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U70">
         <v>3</v>
@@ -11752,19 +11752,19 @@
         <v>1.05</v>
       </c>
       <c r="Y70">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z70">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA70">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB70">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC70">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD70">
         <v>1.18</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK70">
         <v>1.44</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="O2">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P2">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="S2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T2">
         <v>4.5</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z2">
         <v>6.4</v>
@@ -686,13 +686,13 @@
         <v>1.78</v>
       </c>
       <c r="AE2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF2">
         <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK2">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.45</v>
+        <v>5.04</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>5.74</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -831,10 +831,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
         <v>1.98</v>
@@ -849,7 +849,7 @@
         <v>1.24</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
         <v>1.95</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.21</v>
+        <v>2.06</v>
       </c>
       <c r="AK3">
         <v>1.1</v>
@@ -964,10 +964,10 @@
         <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -985,13 +985,13 @@
         <v>4.3</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y4">
         <v>1.61</v>
@@ -1006,7 +1006,7 @@
         <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD4">
         <v>1.06</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O7">
         <v>3.45</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
         <v>2.07</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U7">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1486,28 +1486,28 @@
         <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC7">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
         <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>4.74</v>
       </c>
       <c r="Q8">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.3</v>
+      </c>
+      <c r="Z8">
+        <v>2.97</v>
+      </c>
+      <c r="AA8">
+        <v>2.02</v>
+      </c>
+      <c r="AB8">
+        <v>1.77</v>
+      </c>
+      <c r="AC8">
+        <v>3.34</v>
+      </c>
+      <c r="AD8">
         <v>1.28</v>
       </c>
-      <c r="W8">
-        <v>1.01</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.43</v>
-      </c>
-      <c r="Z8">
-        <v>2.62</v>
-      </c>
-      <c r="AA8">
-        <v>2.37</v>
-      </c>
-      <c r="AB8">
-        <v>1.57</v>
-      </c>
-      <c r="AC8">
-        <v>4.15</v>
-      </c>
-      <c r="AD8">
-        <v>1.16</v>
-      </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK8">
-        <v>1.54</v>
+        <v>2.09</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>4.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="AD9">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>2.09</v>
+        <v>1.54</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="O24">
         <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="Q24">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R24">
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U24">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
         <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AB24">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AD24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG24">
         <v>1.85</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="O25">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="P25">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S25">
         <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
         <v>1.3</v>
@@ -4417,10 +4417,10 @@
         <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z25">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AA25">
         <v>2.38</v>
@@ -4429,7 +4429,7 @@
         <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
         <v>1.2</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="O28">
         <v>3.1</v>
@@ -4906,19 +4906,19 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA28">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
         <v>1.24</v>
@@ -7327,13 +7327,13 @@
         <v>12</v>
       </c>
       <c r="Q43">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="R43">
         <v>2.8</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
         <v>3.5</v>
@@ -7342,10 +7342,10 @@
         <v>2.21</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7357,16 +7357,16 @@
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB43">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC43">
         <v>2.38</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
         <v>1.18</v>
@@ -7391,7 +7391,7 @@
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
+        <v>3.8</v>
+      </c>
+      <c r="P46">
+        <v>2.73</v>
+      </c>
+      <c r="Q46">
+        <v>2.55</v>
+      </c>
+      <c r="R46">
+        <v>2.55</v>
+      </c>
+      <c r="S46">
+        <v>1.2</v>
+      </c>
+      <c r="T46">
         <v>4</v>
       </c>
-      <c r="P46">
-        <v>2.27</v>
-      </c>
-      <c r="Q46">
-        <v>2.6</v>
-      </c>
-      <c r="R46">
+      <c r="U46">
+        <v>2</v>
+      </c>
+      <c r="V46">
+        <v>1.7</v>
+      </c>
+      <c r="W46">
+        <v>1.17</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.07</v>
+      </c>
+      <c r="Z46">
+        <v>5.9</v>
+      </c>
+      <c r="AA46">
+        <v>1.43</v>
+      </c>
+      <c r="AB46">
+        <v>2.7</v>
+      </c>
+      <c r="AC46">
+        <v>2.04</v>
+      </c>
+      <c r="AD46">
+        <v>1.75</v>
+      </c>
+      <c r="AE46">
+        <v>1.29</v>
+      </c>
+      <c r="AF46">
+        <v>1.36</v>
+      </c>
+      <c r="AG46">
         <v>2.75</v>
       </c>
-      <c r="S46">
-        <v>1.11</v>
-      </c>
-      <c r="T46">
-        <v>5.1</v>
-      </c>
-      <c r="U46">
-        <v>1.75</v>
-      </c>
-      <c r="V46">
-        <v>1.95</v>
-      </c>
-      <c r="W46">
-        <v>1.25</v>
-      </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.05</v>
-      </c>
-      <c r="Z46">
-        <v>8.5</v>
-      </c>
-      <c r="AA46">
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.22</v>
       </c>
-      <c r="AB46">
-        <v>3.5</v>
-      </c>
-      <c r="AC46">
-        <v>1.73</v>
-      </c>
-      <c r="AD46">
-        <v>1.96</v>
-      </c>
-      <c r="AE46">
-        <v>1.4</v>
-      </c>
-      <c r="AF46">
-        <v>1.29</v>
-      </c>
-      <c r="AG46">
-        <v>3.2</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.21</v>
-      </c>
       <c r="AK46">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R47">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S47">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="AA47">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AB47">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC47">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AD47">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AE47">
+        <v>1.4</v>
+      </c>
+      <c r="AF47">
         <v>1.29</v>
       </c>
-      <c r="AF47">
-        <v>1.36</v>
-      </c>
       <c r="AG47">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8471,19 +8471,19 @@
         <v>3.24</v>
       </c>
       <c r="R50">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="S50">
         <v>1.31</v>
       </c>
       <c r="T50">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W50">
         <v>1.07</v>
@@ -8495,13 +8495,13 @@
         <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
         <v>2.68</v>
@@ -8532,7 +8532,7 @@
         <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q51">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="V51">
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="AA51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>2.95</v>
+        <v>3.33</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AG51">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q52">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA52">
         <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.78</v>
+        <v>2.98</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
+        <v>2.09</v>
+      </c>
+      <c r="Q53">
         <v>3.7</v>
       </c>
-      <c r="Q53">
-        <v>2.36</v>
-      </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U53">
+        <v>2.34</v>
+      </c>
+      <c r="V53">
+        <v>1.51</v>
+      </c>
+      <c r="W53">
+        <v>1.08</v>
+      </c>
+      <c r="X53">
+        <v>1.02</v>
+      </c>
+      <c r="Y53">
+        <v>1.21</v>
+      </c>
+      <c r="Z53">
+        <v>3.85</v>
+      </c>
+      <c r="AA53">
+        <v>1.76</v>
+      </c>
+      <c r="AB53">
+        <v>2.08</v>
+      </c>
+      <c r="AC53">
         <v>2.88</v>
       </c>
-      <c r="V53">
-        <v>1.42</v>
-      </c>
-      <c r="W53">
-        <v>1.07</v>
-      </c>
-      <c r="X53">
-        <v>1.04</v>
-      </c>
-      <c r="Y53">
-        <v>1.24</v>
-      </c>
-      <c r="Z53">
-        <v>3.65</v>
-      </c>
-      <c r="AA53">
-        <v>1.8</v>
-      </c>
-      <c r="AB53">
-        <v>1.9</v>
-      </c>
-      <c r="AC53">
-        <v>3.26</v>
-      </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11070,28 +11070,28 @@
         <v>1.44</v>
       </c>
       <c r="O66">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P66">
-        <v>6.85</v>
+        <v>7.2</v>
       </c>
       <c r="Q66">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R66">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U66">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W66">
         <v>1.12</v>
@@ -11100,31 +11100,31 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z66">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA66">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB66">
         <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD66">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE66">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF66">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O68">
         <v>3.3</v>
       </c>
       <c r="P68">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="R68">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U68">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11429,13 +11429,13 @@
         <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA68">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB68">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
         <v>2.95</v>
@@ -11444,13 +11444,13 @@
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,26 +794,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>5.04</v>
+        <v>4.73</v>
       </c>
       <c r="O3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>5.52</v>
       </c>
       <c r="R3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
         <v>2.8</v>
@@ -831,31 +831,31 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
         <v>2.97</v>
       </c>
       <c r="AA3">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB3">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -864,41 +864,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AK3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1145,28 +1145,28 @@
         <v>2.75</v>
       </c>
       <c r="U5">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="V5">
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA5">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
         <v>3.6</v>
@@ -1175,13 +1175,13 @@
         <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>8.300000000000001</v>
+        <v>6.68</v>
       </c>
       <c r="R6">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S6">
         <v>1.25</v>
@@ -1308,43 +1308,43 @@
         <v>3.7</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.85</v>
+        <v>4.45</v>
       </c>
       <c r="AA6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB6">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AC6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AD6">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AE6">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O7">
         <v>3.45</v>
@@ -1459,16 +1459,16 @@
         <v>3.45</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R7">
         <v>2.07</v>
       </c>
       <c r="S7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
         <v>2.42</v>
@@ -1480,7 +1480,7 @@
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.19</v>
@@ -1489,16 +1489,16 @@
         <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB7">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AD7">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
@@ -1507,7 +1507,7 @@
         <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O8">
         <v>3.45</v>
       </c>
       <c r="P8">
-        <v>4.74</v>
+        <v>4.9</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R8">
         <v>2.09</v>
@@ -1646,13 +1646,13 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA8">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB8">
         <v>1.77</v>
@@ -1661,7 +1661,7 @@
         <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
         <v>1.05</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
         <v>2.09</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="R9">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="S9">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC9">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q10">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
         <v>2.18</v>
@@ -1957,7 +1957,7 @@
         <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U10">
         <v>2.6</v>
@@ -1978,25 +1978,25 @@
         <v>3.55</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB10">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
         <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
         <v>3.93</v>
@@ -2283,13 +2283,13 @@
         <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -2301,7 +2301,7 @@
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AA12">
         <v>2.19</v>
@@ -2310,10 +2310,10 @@
         <v>1.69</v>
       </c>
       <c r="AC12">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
+        <v>2.6</v>
+      </c>
+      <c r="O13">
+        <v>3.1</v>
+      </c>
+      <c r="P13">
         <v>2.4</v>
-      </c>
-      <c r="O13">
-        <v>3.14</v>
-      </c>
-      <c r="P13">
-        <v>2.65</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
         <v>1.07</v>
@@ -2461,10 +2461,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="O17">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>4.95</v>
+        <v>4.44</v>
       </c>
       <c r="R17">
         <v>2.06</v>
       </c>
       <c r="S17">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="U17">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB17">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG17">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="O20">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="P20">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q20">
         <v>5.4</v>
@@ -3587,13 +3587,13 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
         <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
         <v>3.8</v>
@@ -3738,10 +3738,10 @@
         <v>6.5</v>
       </c>
       <c r="P21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Q21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
         <v>2.5</v>
@@ -3759,28 +3759,28 @@
         <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
         <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE21">
         <v>1.15</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
         <v>3.85</v>
@@ -3901,7 +3901,7 @@
         <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
@@ -3910,10 +3910,10 @@
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>2.18</v>
@@ -3928,44 +3928,44 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
+        <v>1.18</v>
+      </c>
+      <c r="Z22">
+        <v>4.05</v>
+      </c>
+      <c r="AA22">
+        <v>1.63</v>
+      </c>
+      <c r="AB22">
+        <v>2.18</v>
+      </c>
+      <c r="AC22">
+        <v>2.49</v>
+      </c>
+      <c r="AD22">
+        <v>1.42</v>
+      </c>
+      <c r="AE22">
         <v>1.2</v>
       </c>
-      <c r="Z22">
-        <v>4.5</v>
-      </c>
-      <c r="AA22">
-        <v>1.6</v>
-      </c>
-      <c r="AB22">
-        <v>2.19</v>
-      </c>
-      <c r="AC22">
-        <v>2.42</v>
-      </c>
-      <c r="AD22">
+      <c r="AF22">
+        <v>1.5</v>
+      </c>
+      <c r="AG22">
+        <v>2.3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.15</v>
-      </c>
-      <c r="AF22">
-        <v>1.47</v>
-      </c>
-      <c r="AG22">
-        <v>2.34</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>1.53</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O24">
         <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q24">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S24">
         <v>1.37</v>
@@ -4242,7 +4242,7 @@
         <v>2.71</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V24">
         <v>1.4</v>
@@ -4275,7 +4275,7 @@
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
         <v>1.85</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
@@ -4565,7 +4565,7 @@
         <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U26">
         <v>2.88</v>
@@ -4574,10 +4574,10 @@
         <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
         <v>1.3</v>
@@ -4601,10 +4601,10 @@
         <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T27">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="V27">
         <v>1.35</v>
@@ -4740,7 +4740,7 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.32</v>
@@ -4749,13 +4749,13 @@
         <v>2.88</v>
       </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD27">
         <v>1.22</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q29">
         <v>2.85</v>
       </c>
       <c r="R29">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S29">
         <v>1.25</v>
@@ -5063,7 +5063,7 @@
         <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.04</v>
@@ -5072,7 +5072,7 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
         <v>1.66</v>
@@ -5691,16 +5691,16 @@
         <v>1.58</v>
       </c>
       <c r="O33">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5733,7 +5733,7 @@
         <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
@@ -5854,13 +5854,13 @@
         <v>1.44</v>
       </c>
       <c r="O34">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
         <v>7.1</v>
       </c>
       <c r="Q34">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R34">
         <v>2.5</v>
@@ -5887,10 +5887,10 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
         <v>2.4</v>
@@ -6343,7 +6343,7 @@
         <v>1.79</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P37">
         <v>3.8</v>
@@ -6352,16 +6352,16 @@
         <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
         <v>1.5</v>
@@ -6379,19 +6379,19 @@
         <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AC37">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="AD37">
         <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U38">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V38">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W38">
         <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y38">
         <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AA38">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB38">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC38">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="AD38">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE38">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q39">
         <v>2.3</v>
       </c>
       <c r="R39">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V39">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W39">
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
         <v>1.41</v>
       </c>
       <c r="Z39">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AA39">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB39">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC39">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AD39">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AG39">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,31 +7318,31 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="O43">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
       </c>
       <c r="R43">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
         <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
         <v>1.14</v>
@@ -7357,25 +7357,25 @@
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB43">
         <v>2.3</v>
       </c>
       <c r="AC43">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AD43">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
         <v>2.2</v>
       </c>
       <c r="AG43">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O45">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
-        <v>6.85</v>
+        <v>7.2</v>
       </c>
       <c r="Q45">
         <v>1.88</v>
@@ -7662,7 +7662,7 @@
         <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U45">
         <v>2.38</v>
@@ -7671,31 +7671,31 @@
         <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
         <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD45">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE45">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
         <v>1.84</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="Q46">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R46">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z46">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="AA46">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC46">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AD46">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AE46">
+        <v>1.4</v>
+      </c>
+      <c r="AF46">
         <v>1.29</v>
       </c>
-      <c r="AF46">
-        <v>1.36</v>
-      </c>
       <c r="AG46">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O47">
+        <v>3.8</v>
+      </c>
+      <c r="P47">
+        <v>2.73</v>
+      </c>
+      <c r="Q47">
+        <v>2.55</v>
+      </c>
+      <c r="R47">
+        <v>2.55</v>
+      </c>
+      <c r="S47">
+        <v>1.2</v>
+      </c>
+      <c r="T47">
         <v>4</v>
       </c>
-      <c r="P47">
-        <v>2.27</v>
-      </c>
-      <c r="Q47">
-        <v>2.6</v>
-      </c>
-      <c r="R47">
+      <c r="U47">
+        <v>2</v>
+      </c>
+      <c r="V47">
+        <v>1.7</v>
+      </c>
+      <c r="W47">
+        <v>1.17</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.07</v>
+      </c>
+      <c r="Z47">
+        <v>5.9</v>
+      </c>
+      <c r="AA47">
+        <v>1.43</v>
+      </c>
+      <c r="AB47">
+        <v>2.7</v>
+      </c>
+      <c r="AC47">
+        <v>2.04</v>
+      </c>
+      <c r="AD47">
+        <v>1.75</v>
+      </c>
+      <c r="AE47">
+        <v>1.29</v>
+      </c>
+      <c r="AF47">
+        <v>1.36</v>
+      </c>
+      <c r="AG47">
         <v>2.75</v>
       </c>
-      <c r="S47">
-        <v>1.11</v>
-      </c>
-      <c r="T47">
-        <v>5.1</v>
-      </c>
-      <c r="U47">
-        <v>1.75</v>
-      </c>
-      <c r="V47">
-        <v>1.95</v>
-      </c>
-      <c r="W47">
-        <v>1.25</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.05</v>
-      </c>
-      <c r="Z47">
-        <v>8.5</v>
-      </c>
-      <c r="AA47">
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.22</v>
       </c>
-      <c r="AB47">
-        <v>3.5</v>
-      </c>
-      <c r="AC47">
-        <v>1.73</v>
-      </c>
-      <c r="AD47">
-        <v>1.96</v>
-      </c>
-      <c r="AE47">
-        <v>1.4</v>
-      </c>
-      <c r="AF47">
-        <v>1.29</v>
-      </c>
-      <c r="AG47">
-        <v>3.2</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.21</v>
-      </c>
       <c r="AK47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q49">
         <v>3.7</v>
@@ -8314,40 +8314,40 @@
         <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U49">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA49">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB49">
         <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>3.84</v>
+        <v>3.69</v>
       </c>
       <c r="AD49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
         <v>1.74</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>3.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q51">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="R51">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U51">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>3.33</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="Q53">
-        <v>3.7</v>
+        <v>2.43</v>
       </c>
       <c r="R53">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="U53">
-        <v>2.34</v>
+        <v>2.87</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA53">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC53">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG53">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,22 +9274,22 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O55">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="P55">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q55">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R55">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
         <v>3.3</v>
@@ -9301,7 +9301,7 @@
         <v>1.58</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
         <v>1.03</v>
@@ -9313,25 +9313,25 @@
         <v>5</v>
       </c>
       <c r="AA55">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AC55">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD55">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF55">
         <v>2</v>
       </c>
       <c r="AG55">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="Q56">
         <v>2.8</v>
@@ -9461,7 +9461,7 @@
         <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
         <v>1.1</v>
@@ -9482,10 +9482,10 @@
         <v>1.98</v>
       </c>
       <c r="AC56">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="AD56">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE56">
         <v>1.14</v>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O57">
         <v>3.8</v>
       </c>
       <c r="P57">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
       </c>
       <c r="R57">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9636,10 +9636,10 @@
         <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
         <v>2.23</v>
@@ -9648,16 +9648,16 @@
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -982,7 +982,7 @@
         <v>2.1</v>
       </c>
       <c r="U4">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="V4">
         <v>1.14</v>
@@ -1006,7 +1006,7 @@
         <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD4">
         <v>1.06</v>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,14 +1113,14 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,23 +1267,23 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "29", "68"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "26", "66"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "90+5"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,106 +1602,106 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q8">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="R8">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="S8">
+        <v>1.46</v>
+      </c>
+      <c r="T8">
+        <v>2.5</v>
+      </c>
+      <c r="U8">
+        <v>3.22</v>
+      </c>
+      <c r="V8">
+        <v>1.29</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
         <v>1.41</v>
       </c>
-      <c r="T8">
-        <v>2.78</v>
-      </c>
-      <c r="U8">
-        <v>2.78</v>
-      </c>
-      <c r="V8">
-        <v>1.38</v>
-      </c>
-      <c r="W8">
-        <v>1.06</v>
-      </c>
-      <c r="X8">
+      <c r="Z8">
+        <v>2.7</v>
+      </c>
+      <c r="AA8">
+        <v>2.29</v>
+      </c>
+      <c r="AB8">
+        <v>1.64</v>
+      </c>
+      <c r="AC8">
+        <v>4.23</v>
+      </c>
+      <c r="AD8">
+        <v>1.17</v>
+      </c>
+      <c r="AE8">
         <v>1.02</v>
       </c>
-      <c r="Y8">
-        <v>1.29</v>
-      </c>
-      <c r="Z8">
-        <v>3.04</v>
-      </c>
-      <c r="AA8">
-        <v>2.01</v>
-      </c>
-      <c r="AB8">
-        <v>1.77</v>
-      </c>
-      <c r="AC8">
-        <v>3.34</v>
-      </c>
-      <c r="AD8">
-        <v>1.24</v>
-      </c>
-      <c r="AE8">
-        <v>1.05</v>
-      </c>
       <c r="AF8">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -1744,22 +1744,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,72 +1772,72 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="O9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="R9">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>3.22</v>
+        <v>2.78</v>
       </c>
       <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
         <v>1.29</v>
       </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.41</v>
-      </c>
       <c r="Z9">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>4.23</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1846,37 +1846,37 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "80", "90+2"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2082,30 +2082,30 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
         <v>2.61</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="P11">
         <v>2.55</v>
@@ -2123,25 +2123,25 @@
         <v>2.75</v>
       </c>
       <c r="U11">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
         <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB11">
         <v>1.62</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "66"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2274,19 +2274,19 @@
         <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="R12">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
         <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V12">
         <v>1.34</v>
@@ -2298,10 +2298,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z12">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="AA12">
         <v>2.19</v>
@@ -2310,19 +2310,19 @@
         <v>1.69</v>
       </c>
       <c r="AC12">
-        <v>4.02</v>
+        <v>3.72</v>
       </c>
       <c r="AD12">
         <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2440,13 +2440,13 @@
         <v>2.75</v>
       </c>
       <c r="R13">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="U13">
         <v>2.85</v>
@@ -2461,7 +2461,7 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
         <v>2.63</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
         <v>1.49</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="R16">
         <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U16">
         <v>2.8</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.67</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.77</v>
+        <v>3.48</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
         <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V17">
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC17">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="P20">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q20">
         <v>5.4</v>
       </c>
       <c r="R20">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S20">
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
         <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
         <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
         <v>2</v>
@@ -3623,10 +3623,10 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK20">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,16 +3741,16 @@
         <v>11.5</v>
       </c>
       <c r="Q21">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
         <v>2.38</v>
@@ -3762,31 +3762,31 @@
         <v>1.12</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
         <v>1.57</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AK21">
         <v>3.85</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q22">
         <v>2.55</v>
@@ -3916,40 +3916,40 @@
         <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="V22">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
         <v>4.05</v>
       </c>
       <c r="AA22">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB22">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AC22">
         <v>2.49</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
         <v>2.3</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.53</v>
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="P23">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q23">
         <v>6</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
         <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB23">
         <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE23">
+        <v>1.13</v>
+      </c>
+      <c r="AF23">
+        <v>1.75</v>
+      </c>
+      <c r="AG23">
+        <v>1.91</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.19</v>
+      </c>
+      <c r="AK23">
         <v>1.14</v>
-      </c>
-      <c r="AF23">
-        <v>1.8</v>
-      </c>
-      <c r="AG23">
-        <v>1.93</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.2</v>
-      </c>
-      <c r="AK23">
-        <v>1.11</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>1.6</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P24">
-        <v>4.8</v>
+        <v>4.89</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
@@ -4239,7 +4239,7 @@
         <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2.79</v>
@@ -4248,10 +4248,10 @@
         <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.25</v>
@@ -4260,22 +4260,22 @@
         <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB24">
         <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG24">
         <v>1.85</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P25">
         <v>2.77</v>
       </c>
       <c r="Q25">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="S25">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T25">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
+        <v>1.02</v>
+      </c>
+      <c r="X25">
         <v>1.05</v>
       </c>
-      <c r="X25">
-        <v>1.07</v>
-      </c>
       <c r="Y25">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="Z25">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA25">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
         <v>1.96</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="O26">
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
@@ -4562,34 +4562,34 @@
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="U26">
         <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
         <v>3.9</v>
@@ -4601,10 +4601,10 @@
         <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4716,22 +4716,22 @@
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="Q27">
         <v>2.88</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
         <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="V27">
         <v>1.35</v>
@@ -4740,16 +4740,16 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA27">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
         <v>1.7</v>
@@ -4764,10 +4764,10 @@
         <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
         <v>1.91</v>
@@ -4894,7 +4894,7 @@
         <v>2.75</v>
       </c>
       <c r="U28">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="V28">
         <v>1.3</v>
@@ -4903,34 +4903,34 @@
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA28">
         <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.92</v>
       </c>
       <c r="AD28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
         <v>1.25</v>
@@ -5039,13 +5039,13 @@
         <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R29">
         <v>2.42</v>
@@ -5054,13 +5054,13 @@
         <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W29">
         <v>1.08</v>
@@ -5069,25 +5069,25 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
         <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AC29">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF29">
         <v>1.55</v>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="R30">
         <v>2.37</v>
@@ -5217,7 +5217,7 @@
         <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="U30">
         <v>2.45</v>
@@ -5229,7 +5229,7 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
@@ -5238,19 +5238,19 @@
         <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC30">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AD30">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="P31">
         <v>2.81</v>
       </c>
       <c r="Q31">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="R31">
         <v>2.37</v>
       </c>
       <c r="S31">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.06</v>
@@ -5395,7 +5395,7 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
         <v>4.3</v>
@@ -5407,13 +5407,13 @@
         <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AD31">
         <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK31">
         <v>1.57</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O32">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q32">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R32">
         <v>3.2</v>
       </c>
       <c r="S32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="U32">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="V32">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="W32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5561,25 +5561,25 @@
         <v>1.01</v>
       </c>
       <c r="Z32">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="AA32">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AB32">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AC32">
         <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
         <v>2.05</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>4.27</v>
+        <v>5.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,13 +5691,13 @@
         <v>1.58</v>
       </c>
       <c r="O33">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>6.08</v>
+        <v>5.5</v>
       </c>
       <c r="Q33">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="R33">
         <v>2.65</v>
@@ -5712,7 +5712,7 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W33">
         <v>1.09</v>
@@ -5739,7 +5739,7 @@
         <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5854,13 +5854,13 @@
         <v>1.44</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="P34">
-        <v>7.1</v>
+        <v>7.21</v>
       </c>
       <c r="Q34">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R34">
         <v>2.5</v>
@@ -5881,31 +5881,31 @@
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA34">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
+        <v>2.3</v>
+      </c>
+      <c r="AC34">
         <v>2.4</v>
-      </c>
-      <c r="AC34">
-        <v>2.28</v>
       </c>
       <c r="AD34">
         <v>1.54</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
         <v>1.98</v>
@@ -6014,55 +6014,55 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O35">
         <v>4.2</v>
       </c>
       <c r="P35">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q35">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="U35">
         <v>2.43</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB35">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
         <v>1.12</v>
@@ -6071,7 +6071,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="P37">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6355,22 +6355,22 @@
         <v>2.27</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T37">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.18</v>
@@ -6379,16 +6379,16 @@
         <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB37">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="AC37">
         <v>2.44</v>
       </c>
       <c r="AD37">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE37">
         <v>1.2</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
         <v>1.95</v>
@@ -6503,46 +6503,46 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T38">
+        <v>2.39</v>
+      </c>
+      <c r="U38">
+        <v>3.3</v>
+      </c>
+      <c r="V38">
+        <v>1.29</v>
+      </c>
+      <c r="W38">
+        <v>1.03</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.36</v>
+      </c>
+      <c r="Z38">
         <v>2.75</v>
       </c>
-      <c r="U38">
-        <v>3</v>
-      </c>
-      <c r="V38">
-        <v>1.3</v>
-      </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.07</v>
-      </c>
-      <c r="Y38">
-        <v>1.41</v>
-      </c>
-      <c r="Z38">
-        <v>2.74</v>
-      </c>
       <c r="AA38">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB38">
         <v>1.59</v>
@@ -6551,13 +6551,13 @@
         <v>3.88</v>
       </c>
       <c r="AD38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG38">
         <v>1.73</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK38">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="O39">
         <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.9</v>
+        <v>5.11</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S39">
         <v>1.5</v>
       </c>
       <c r="T39">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="U39">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6705,13 +6705,13 @@
         <v>2.52</v>
       </c>
       <c r="AA39">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC39">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD39">
         <v>1.15</v>
@@ -6720,10 +6720,10 @@
         <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q41">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="U41">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.05</v>
@@ -7028,10 +7028,10 @@
         <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB41">
         <v>1.88</v>
@@ -7040,16 +7040,16 @@
         <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="O43">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="R43">
         <v>2.75</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U43">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC43">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD43">
         <v>1.49</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AG43">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7647,61 +7647,61 @@
         <v>1.36</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q45">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R45">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
         <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W45">
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB45">
         <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD45">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE45">
         <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q46">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="R46">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S46">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T46">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U46">
         <v>1.75</v>
       </c>
       <c r="V46">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z46">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA46">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AB46">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AC46">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AD46">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AE46">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF46">
         <v>1.29</v>
       </c>
       <c r="AG46">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P47">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="Q47">
         <v>2.55</v>
@@ -7988,46 +7988,46 @@
         <v>1.2</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V47">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z47">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA47">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB47">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AC47">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AD47">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG47">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
+        <v>3.2</v>
+      </c>
+      <c r="O49">
         <v>3.1</v>
       </c>
-      <c r="O49">
-        <v>3</v>
-      </c>
       <c r="P49">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q49">
         <v>3.7</v>
@@ -8311,25 +8311,25 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="U49">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z49">
         <v>3.25</v>
@@ -8344,16 +8344,16 @@
         <v>3.69</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE49">
         <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG49">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
+        <v>1.75</v>
+      </c>
+      <c r="O52">
+        <v>3.4</v>
+      </c>
+      <c r="P52">
+        <v>3.9</v>
+      </c>
+      <c r="Q52">
+        <v>2.43</v>
+      </c>
+      <c r="R52">
+        <v>2.14</v>
+      </c>
+      <c r="S52">
+        <v>1.36</v>
+      </c>
+      <c r="T52">
         <v>3</v>
       </c>
-      <c r="O52">
-        <v>3.3</v>
-      </c>
-      <c r="P52">
-        <v>2.05</v>
-      </c>
-      <c r="Q52">
-        <v>3.48</v>
-      </c>
-      <c r="R52">
-        <v>2.19</v>
-      </c>
-      <c r="S52">
-        <v>1.34</v>
-      </c>
-      <c r="T52">
-        <v>3.25</v>
-      </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="V52">
         <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>3.33</v>
       </c>
       <c r="AD52">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AG52">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q53">
-        <v>2.43</v>
+        <v>3.48</v>
       </c>
       <c r="R53">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC53">
-        <v>3.33</v>
+        <v>2.95</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="O55">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P55">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q55">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="R55">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9295,43 +9295,43 @@
         <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V55">
         <v>1.58</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
         <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AA55">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB55">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AC55">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD55">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE55">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF55">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK55">
-        <v>3.65</v>
+        <v>4.56</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P56">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q56">
         <v>2.8</v>
@@ -9452,16 +9452,16 @@
         <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
         <v>1.1</v>
@@ -9470,22 +9470,22 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z56">
         <v>3.9</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
         <v>1.98</v>
       </c>
       <c r="AC56">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD56">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE56">
         <v>1.14</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,61 +9600,61 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O57">
         <v>3.8</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
       </c>
       <c r="R57">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z57">
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AB57">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
         <v>2.3</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,16 +9766,16 @@
         <v>1.19</v>
       </c>
       <c r="O58">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="P58">
         <v>9</v>
       </c>
       <c r="Q58">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R58">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="S58">
         <v>1.13</v>
@@ -9784,10 +9784,10 @@
         <v>5.5</v>
       </c>
       <c r="U58">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V58">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="W58">
         <v>1.3</v>
@@ -9802,10 +9802,10 @@
         <v>9</v>
       </c>
       <c r="AA58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AB58">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AC58">
         <v>1.63</v>
@@ -9814,13 +9814,13 @@
         <v>2.05</v>
       </c>
       <c r="AE58">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AK58">
         <v>3.7</v>
@@ -10252,55 +10252,55 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="O61">
         <v>3.2</v>
       </c>
       <c r="P61">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q61">
         <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U61">
         <v>2.8</v>
       </c>
       <c r="V61">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z61">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA61">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB61">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC61">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD61">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE61">
         <v>1.07</v>
@@ -10309,7 +10309,7 @@
         <v>1.71</v>
       </c>
       <c r="AG61">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10581,61 +10581,61 @@
         <v>1.8</v>
       </c>
       <c r="O63">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="P63">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="Q63">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="R63">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V63">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W63">
         <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
         <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AA63">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB63">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC63">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD63">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
         <v>1.07</v>
       </c>
       <c r="AF63">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG63">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
+        <v>3.1</v>
+      </c>
+      <c r="P67">
+        <v>3.51</v>
+      </c>
+      <c r="Q67">
+        <v>2.63</v>
+      </c>
+      <c r="R67">
+        <v>2.09</v>
+      </c>
+      <c r="S67">
+        <v>1.35</v>
+      </c>
+      <c r="T67">
         <v>3</v>
       </c>
-      <c r="P67">
-        <v>2.9</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA67">
         <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O71">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q71">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="R71">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S71">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T71">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="U71">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V71">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z71">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="AA71">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB71">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD71">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE71">
         <v>1.05</v>
       </c>
       <c r="AF71">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG71">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-09-14.xlsx
+++ b/jogos_2026-09-14.xlsx
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2254,14 +2254,14 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,16 +2344,16 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "49", "89"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2587,111 +2587,111 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["11"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,139 +2722,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
+        <v>11</v>
+      </c>
+      <c r="O15">
+        <v>6.25</v>
+      </c>
+      <c r="P15">
+        <v>1.17</v>
+      </c>
+      <c r="Q15">
+        <v>7.5</v>
+      </c>
+      <c r="R15">
+        <v>3.25</v>
+      </c>
+      <c r="S15">
+        <v>1.15</v>
+      </c>
+      <c r="T15">
+        <v>4.8</v>
+      </c>
+      <c r="U15">
+        <v>1.75</v>
+      </c>
+      <c r="V15">
         <v>1.95</v>
       </c>
-      <c r="O15">
+      <c r="W15">
+        <v>1.29</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.06</v>
+      </c>
+      <c r="Z15">
+        <v>9</v>
+      </c>
+      <c r="AA15">
+        <v>1.21</v>
+      </c>
+      <c r="AB15">
+        <v>3.58</v>
+      </c>
+      <c r="AC15">
+        <v>1.56</v>
+      </c>
+      <c r="AD15">
+        <v>2.15</v>
+      </c>
+      <c r="AE15">
+        <v>1.54</v>
+      </c>
+      <c r="AF15">
+        <v>1.62</v>
+      </c>
+      <c r="AG15">
+        <v>2.15</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>["42", "44", "50", "89"]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.1</v>
+      </c>
+      <c r="AK15">
+        <v>1.04</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15">
+        <v>15</v>
+      </c>
+      <c r="AO15">
+        <v>2</v>
+      </c>
+      <c r="AP15">
+        <v>23</v>
+      </c>
+      <c r="AQ15">
+        <v>0.29</v>
+      </c>
+      <c r="AR15">
         <v>3.2</v>
       </c>
-      <c r="P15">
-        <v>3.61</v>
-      </c>
-      <c r="Q15">
-        <v>2.62</v>
-      </c>
-      <c r="R15">
-        <v>2.08</v>
-      </c>
-      <c r="S15">
-        <v>1.38</v>
-      </c>
-      <c r="T15">
-        <v>2.88</v>
-      </c>
-      <c r="U15">
-        <v>2.75</v>
-      </c>
-      <c r="V15">
-        <v>1.35</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>1.26</v>
-      </c>
-      <c r="Z15">
-        <v>3.2</v>
-      </c>
-      <c r="AA15">
-        <v>1.93</v>
-      </c>
-      <c r="AB15">
-        <v>1.76</v>
-      </c>
-      <c r="AC15">
-        <v>3.28</v>
-      </c>
-      <c r="AD15">
-        <v>1.25</v>
-      </c>
-      <c r="AE15">
-        <v>1.1</v>
-      </c>
-      <c r="AF15">
-        <v>1.72</v>
-      </c>
-      <c r="AG15">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.24</v>
-      </c>
-      <c r="AK15">
-        <v>1.63</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
       <c r="AS15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2906,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "90+5"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "85"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3072,11 +3072,11 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "90+3"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,22 +3211,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3239,111 +3239,111 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="Q18">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="R18">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="U18">
+        <v>2.14</v>
+      </c>
+      <c r="V18">
+        <v>1.6</v>
+      </c>
+      <c r="W18">
+        <v>1.17</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.11</v>
+      </c>
+      <c r="Z18">
+        <v>5.5</v>
+      </c>
+      <c r="AA18">
+        <v>1.45</v>
+      </c>
+      <c r="AB18">
+        <v>2.53</v>
+      </c>
+      <c r="AC18">
+        <v>2.23</v>
+      </c>
+      <c r="AD18">
+        <v>1.6</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.53</v>
+      </c>
+      <c r="AG18">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["16", "35"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>2.18</v>
+      </c>
+      <c r="AK18">
+        <v>1.07</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
         <v>3</v>
       </c>
-      <c r="V18">
-        <v>1.33</v>
-      </c>
-      <c r="W18">
-        <v>1.03</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>1.33</v>
-      </c>
-      <c r="Z18">
-        <v>2.88</v>
-      </c>
-      <c r="AA18">
-        <v>2</v>
-      </c>
-      <c r="AB18">
-        <v>1.67</v>
-      </c>
-      <c r="AC18">
-        <v>3.9</v>
-      </c>
-      <c r="AD18">
-        <v>1.22</v>
-      </c>
-      <c r="AE18">
-        <v>1.04</v>
-      </c>
-      <c r="AF18">
-        <v>1.9</v>
-      </c>
-      <c r="AG18">
-        <v>1.8</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.21</v>
-      </c>
-      <c r="AK18">
-        <v>1.83</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,111 +3402,111 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>4.59</v>
+        <v>1.8</v>
       </c>
       <c r="O19">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>4.58</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>3.52</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19">
+        <v>1.7</v>
+      </c>
+      <c r="AC19">
+        <v>3.9</v>
+      </c>
+      <c r="AD19">
+        <v>1.22</v>
+      </c>
+      <c r="AE19">
+        <v>1.04</v>
+      </c>
+      <c r="AF19">
+        <v>1.93</v>
+      </c>
+      <c r="AG19">
+        <v>1.78</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>["6", "23", "28"]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>["25"]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.27</v>
+      </c>
+      <c r="AK19">
+        <v>1.83</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>5</v>
+      </c>
+      <c r="AN19">
+        <v>6</v>
+      </c>
+      <c r="AO19">
+        <v>14</v>
+      </c>
+      <c r="AP19">
+        <v>10</v>
+      </c>
+      <c r="AQ19">
+        <v>1.56</v>
+      </c>
+      <c r="AR19">
         <v>1.45</v>
       </c>
-      <c r="AB19">
-        <v>2.41</v>
-      </c>
-      <c r="AC19">
-        <v>2.18</v>
-      </c>
-      <c r="AD19">
-        <v>1.61</v>
-      </c>
-      <c r="AE19">
-        <v>1.2</v>
-      </c>
-      <c r="AF19">
-        <v>1.51</v>
-      </c>
-      <c r="AG19">
-        <v>2.39</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>2.14</v>
-      </c>
-      <c r="AK19">
-        <v>1.17</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
       <c r="AS19">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,23 +3549,23 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "90+3"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "83"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "80"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "35", "45", "64"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -4373,14 +4373,14 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "65"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "58"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "53"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "90+1"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4865,11 +4865,11 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5016,23 +5016,23 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "67"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5191,11 +5191,11 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "90"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5351,14 +5351,14 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "54", "58"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69", "90+1"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "63"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5809,110 +5809,110 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O34">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
-        <v>7.21</v>
+        <v>5.75</v>
       </c>
       <c r="Q34">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="U34">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "34", "44", "83"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -5924,34 +5924,34 @@
         <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,96 +5982,96 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>1.42</v>
+        <v>3.79</v>
       </c>
       <c r="O35">
+        <v>3.5</v>
+      </c>
+      <c r="P35">
+        <v>1.83</v>
+      </c>
+      <c r="Q35">
         <v>4.2</v>
       </c>
-      <c r="P35">
-        <v>5.75</v>
-      </c>
-      <c r="Q35">
-        <v>1.91</v>
-      </c>
       <c r="R35">
+        <v>2.18</v>
+      </c>
+      <c r="S35">
+        <v>1.25</v>
+      </c>
+      <c r="T35">
+        <v>3.32</v>
+      </c>
+      <c r="U35">
         <v>2.29</v>
       </c>
-      <c r="S35">
-        <v>1.3</v>
-      </c>
-      <c r="T35">
-        <v>2.99</v>
-      </c>
-      <c r="U35">
-        <v>2.43</v>
-      </c>
       <c r="V35">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z35">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC35">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6080,41 +6080,41 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "56", "66", "86"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>2.42</v>
+        <v>1.22</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,139 +6145,139 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="P36">
-        <v>1.8</v>
+        <v>4.17</v>
       </c>
       <c r="Q36">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T36">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V36">
+        <v>1.57</v>
+      </c>
+      <c r="W36">
+        <v>1.15</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>4.6</v>
+      </c>
+      <c r="AA36">
+        <v>1.58</v>
+      </c>
+      <c r="AB36">
+        <v>2.47</v>
+      </c>
+      <c r="AC36">
+        <v>2.44</v>
+      </c>
+      <c r="AD36">
         <v>1.6</v>
       </c>
-      <c r="W36">
-        <v>1.11</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.16</v>
-      </c>
-      <c r="Z36">
-        <v>4.2</v>
-      </c>
-      <c r="AA36">
-        <v>1.64</v>
-      </c>
-      <c r="AB36">
-        <v>2.2</v>
-      </c>
-      <c r="AC36">
-        <v>2.49</v>
-      </c>
-      <c r="AD36">
-        <v>1.48</v>
-      </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
         <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "23", "74", "89"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69", "90+2"]</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,25 +6308,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="O37">
-        <v>3.74</v>
+        <v>3.12</v>
       </c>
       <c r="P37">
-        <v>4.17</v>
+        <v>4.01</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R37">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>2.39</v>
       </c>
       <c r="U37">
-        <v>2.27</v>
+        <v>3.3</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA37">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="AB37">
-        <v>2.47</v>
+        <v>1.59</v>
       </c>
       <c r="AC37">
-        <v>2.44</v>
+        <v>3.88</v>
       </c>
       <c r="AD37">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6406,41 +6406,41 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6471,139 +6471,139 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P38">
-        <v>4.01</v>
+        <v>5.11</v>
       </c>
       <c r="Q38">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T38">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="U38">
         <v>3.3</v>
       </c>
       <c r="V38">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W38">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AA38">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AB38">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC38">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AD38">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AG38">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "84"]</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,19 +6634,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -6658,72 +6658,72 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>5.11</v>
+        <v>1.65</v>
       </c>
       <c r="Q39">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="R39">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y39">
+        <v>1.2</v>
+      </c>
+      <c r="Z39">
+        <v>4.2</v>
+      </c>
+      <c r="AA39">
+        <v>1.66</v>
+      </c>
+      <c r="AB39">
+        <v>2.15</v>
+      </c>
+      <c r="AC39">
+        <v>2.52</v>
+      </c>
+      <c r="AD39">
         <v>1.41</v>
       </c>
-      <c r="Z39">
-        <v>2.52</v>
-      </c>
-      <c r="AA39">
-        <v>2.4</v>
-      </c>
-      <c r="AB39">
-        <v>1.5</v>
-      </c>
-      <c r="AC39">
-        <v>4.2</v>
-      </c>
-      <c r="AD39">
-        <v>1.15</v>
-      </c>
       <c r="AE39">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6732,41 +6732,41 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>1.93</v>
+        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6782,31 +6782,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6818,122 +6818,122 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>4.7</v>
+        <v>2.35</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U40">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AB40">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC40">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
         <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
+          <t>["68"]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-14 14:00:00</t>
+          <t>2026-09-14 14:05:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,22 +6960,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -6988,115 +6988,115 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="P41">
-        <v>3.6</v>
+        <v>7.21</v>
       </c>
       <c r="Q41">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB41">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD41">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
+          <t>["2", "44"]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK41">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:00</t>
+          <t>2026-09-14 14:20:00</t>
         </is>
       </c>
     </row>
@@ -7132,36 +7132,36 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -7170,19 +7170,19 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.04</v>
@@ -7191,71 +7191,71 @@
         <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AC42">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
         <v>1.46</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "36", "44", "90"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,26 +7295,26 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "59"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ43">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,39 +7458,39 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
         <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7499,59 +7499,59 @@
         <v>1.38</v>
       </c>
       <c r="T44">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U44">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
         <v>3.15</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
         <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD44">
         <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "56", "78"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "53", "61"]</t>
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
         <v>1.43</v>
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,26 +7621,26 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "24"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "66"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7775,139 +7775,139 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="O46">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P46">
-        <v>2.26</v>
+        <v>2.69</v>
       </c>
       <c r="Q46">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="R46">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U46">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="V46">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="W46">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Z46">
-        <v>8.4</v>
+        <v>6.25</v>
       </c>
       <c r="AA46">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
-        <v>3.58</v>
+        <v>2.83</v>
       </c>
       <c r="AC46">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AD46">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="AE46">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AF46">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG46">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "21", "41", "55", "74", "88"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7938,22 +7938,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -7962,115 +7962,115 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="O47">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P47">
-        <v>2.69</v>
+        <v>2.26</v>
       </c>
       <c r="Q47">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="R47">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S47">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T47">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="W47">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Z47">
-        <v>6.25</v>
+        <v>8.4</v>
       </c>
       <c r="AA47">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AB47">
-        <v>2.83</v>
+        <v>3.58</v>
       </c>
       <c r="AC47">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AD47">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AE47">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AF47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG47">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O48">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="P48">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q48">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="R48">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="S48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T48">
         <v>2.25</v>
       </c>
       <c r="U48">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V48">
         <v>1.21</v>
       </c>
       <c r="W48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y48">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Z48">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AA48">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB48">
         <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.45</v>
+        <v>6.11</v>
       </c>
       <c r="AD48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AG48">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q51">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA51">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>3.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q52">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U52">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB52">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC52">
-        <v>3.33</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
+        <v>1.75</v>
+      </c>
+      <c r="O53">
+        <v>3.4</v>
+      </c>
+      <c r="P53">
+        <v>3.9</v>
+      </c>
+      <c r="Q53">
+        <v>2.43</v>
+      </c>
+      <c r="R53">
+        <v>2.14</v>
+      </c>
+      <c r="S53">
+        <v>1.36</v>
+      </c>
+      <c r="T53">
         <v>3</v>
       </c>
-      <c r="O53">
-        <v>3.3</v>
-      </c>
-      <c r="P53">
-        <v>2.05</v>
-      </c>
-      <c r="Q53">
-        <v>3.48</v>
-      </c>
-      <c r="R53">
-        <v>2.19</v>
-      </c>
-      <c r="S53">
-        <v>1.34</v>
-      </c>
-      <c r="T53">
-        <v>3.25</v>
-      </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC53">
-        <v>2.95</v>
+        <v>3.33</v>
       </c>
       <c r="AD53">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AG53">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,61 +9114,61 @@
         <v>2.37</v>
       </c>
       <c r="O54">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P54">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
       </c>
       <c r="R54">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S54">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U54">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="V54">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z54">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AA54">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC54">
         <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9251,26 +9251,26 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "35", "57", "67", "79"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "16", "90"]</t>
         </is>
       </c>
       <c r="AJ55">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="O58">
-        <v>6.75</v>
+        <v>6.05</v>
       </c>
       <c r="P58">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q58">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="S58">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="U58">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V58">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="W58">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z58">
-        <v>9</v>
+        <v>6.65</v>
       </c>
       <c r="AA58">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AB58">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC58">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD58">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AE58">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AF58">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK58">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="O59">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="P59">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="Q59">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="R59">
         <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T59">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U59">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z59">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA59">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AB59">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="AD59">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF59">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG59">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="O60">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="P60">
-        <v>7.05</v>
+        <v>9.5</v>
       </c>
       <c r="Q60">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="R60">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T60">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U60">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="V60">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X60">
         <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC60">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AD60">
         <v>1.45</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF60">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG60">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>2.78</v>
+        <v>3.36</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="P61">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="R61">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S61">
         <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U61">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V61">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W61">
         <v>1.05</v>
@@ -10285,31 +10285,31 @@
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA61">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC61">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD61">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG61">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AK61">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10578,22 +10578,22 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="P63">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="Q63">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="R63">
         <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T63">
         <v>2.88</v>
@@ -10608,7 +10608,7 @@
         <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
         <v>1.3</v>
@@ -10617,7 +10617,7 @@
         <v>3.2</v>
       </c>
       <c r="AA63">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB63">
         <v>1.65</v>
@@ -10635,7 +10635,7 @@
         <v>1.85</v>
       </c>
       <c r="AG63">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-14 19:30:00</t>
+          <t>2026-09-14 19:05:00</t>
         </is>
       </c>
     </row>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q64">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="R64">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T64">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="U64">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="V64">
         <v>1.35</v>
@@ -10771,34 +10771,34 @@
         <v>1.05</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z64">
-        <v>3.44</v>
+        <v>2.83</v>
       </c>
       <c r="AA64">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB64">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD64">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
         <v>1.07</v>
       </c>
       <c r="AF64">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG64">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O65">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P65">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="Q65">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S65">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="T65">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="U65">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="V65">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X65">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y65">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z65">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AA65">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB65">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC65">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD65">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AK65">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="R67">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U67">
         <v>2.62</v>
@@ -11260,19 +11260,19 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z67">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB67">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC67">
         <v>3.08</v>
@@ -11284,10 +11284,10 @@
         <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O68">
         <v>3.3</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q68">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="U68">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V68">
         <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA68">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB68">
         <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AD68">
         <v>1.36</v>
       </c>
       <c r="AE68">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
         <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O69">
+        <v>4.3</v>
+      </c>
+      <c r="P69">
+        <v>6.8</v>
+      </c>
+      <c r="Q69">
+        <v>1.88</v>
+      </c>
+      <c r="R69">
+        <v>2.64</v>
+      </c>
+      <c r="S69">
+        <v>1.25</v>
+      </c>
+      <c r="T69">
+        <v>3.28</v>
+      </c>
+      <c r="U69">
+        <v>2.19</v>
+      </c>
+      <c r="V69">
+        <v>1.55</v>
+      </c>
+      <c r="W69">
+        <v>1.13</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>1.13</v>
+      </c>
+      <c r="Z69">
         <v>4.5</v>
       </c>
-      <c r="P69">
-        <v>7.6</v>
-      </c>
-      <c r="Q69">
-        <v>1.91</v>
-      </c>
-      <c r="R69">
+      <c r="AA69">
+        <v>1.6</v>
+      </c>
+      <c r="AB69">
         <v>2.3</v>
       </c>
-      <c r="S69">
-        <v>1.3</v>
-      </c>
-      <c r="T69">
-        <v>3.2</v>
-      </c>
-      <c r="U69">
-        <v>2.29</v>
-      </c>
-      <c r="V69">
-        <v>1.48</v>
-      </c>
-      <c r="W69">
-        <v>1.11</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.16</v>
-      </c>
-      <c r="Z69">
-        <v>4.1</v>
-      </c>
-      <c r="AA69">
-        <v>1.72</v>
-      </c>
-      <c r="AB69">
-        <v>2</v>
-      </c>
       <c r="AC69">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AD69">
         <v>1.36</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF69">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG69">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK69">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q70">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R70">
+        <v>1.88</v>
+      </c>
+      <c r="S70">
+        <v>1.53</v>
+      </c>
+      <c r="T70">
+        <v>2.51</v>
+      </c>
+      <c r="U70">
+        <v>3.5</v>
+      </c>
+      <c r="V70">
+        <v>1.25</v>
+      </c>
+      <c r="W70">
+        <v>1.03</v>
+      </c>
+      <c r="X70">
+        <v>1.06</v>
+      </c>
+      <c r="Y70">
+        <v>1.49</v>
+      </c>
+      <c r="Z70">
+        <v>2.41</v>
+      </c>
+      <c r="AA70">
+        <v>2.57</v>
+      </c>
+      <c r="AB70">
+        <v>1.57</v>
+      </c>
+      <c r="AC70">
+        <v>5.25</v>
+      </c>
+      <c r="AD70">
+        <v>1.13</v>
+      </c>
+      <c r="AE70">
+        <v>1.01</v>
+      </c>
+      <c r="AF70">
         <v>2</v>
       </c>
-      <c r="S70">
-        <v>1.49</v>
-      </c>
-      <c r="T70">
-        <v>2.53</v>
-      </c>
-      <c r="U70">
-        <v>3</v>
-      </c>
-      <c r="V70">
-        <v>1.29</v>
-      </c>
-      <c r="W70">
-        <v>1.04</v>
-      </c>
-      <c r="X70">
-        <v>1.05</v>
-      </c>
-      <c r="Y70">
-        <v>1.4</v>
-      </c>
-      <c r="Z70">
-        <v>2.88</v>
-      </c>
-      <c r="AA70">
-        <v>2.29</v>
-      </c>
-      <c r="AB70">
-        <v>1.6</v>
-      </c>
-      <c r="AC70">
-        <v>4.5</v>
-      </c>
-      <c r="AD70">
-        <v>1.18</v>
-      </c>
-      <c r="AE70">
-        <v>1.02</v>
-      </c>
-      <c r="AF70">
-        <v>1.91</v>
-      </c>
       <c r="AG70">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AK70">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O71">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q71">
         <v>2.9</v>
@@ -11897,10 +11897,10 @@
         <v>2.05</v>
       </c>
       <c r="S71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U71">
         <v>2.88</v>
@@ -11921,25 +11921,25 @@
         <v>2.92</v>
       </c>
       <c r="AA71">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB71">
         <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF71">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG71">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK71">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL71">
         <v>0</v>
